--- a/AAII_Financials/Quarterly/KEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KEN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>KEN</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>229000</v>
+      </c>
+      <c r="E8" s="3">
         <v>165000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>147000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>145000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>163000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>121000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>146000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>134800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>353000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>105000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>115000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>104500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>117000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>76000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>89000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>89500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>102000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>85000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>97000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>85000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>94000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>84000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>101000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>365700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>97000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>84000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>93000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>324300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>502000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>459300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>176000</v>
+      </c>
+      <c r="E9" s="3">
         <v>146000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>117000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>122100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>130000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>113000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>110000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>110400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>279000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>93000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>92000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>90200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>93000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>66000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>65000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>69200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>77000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>72000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>68000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>78300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>69000</v>
-      </c>
-      <c r="X9" s="3">
-        <v>71000</v>
       </c>
       <c r="Y9" s="3">
         <v>71000</v>
       </c>
       <c r="Z9" s="3">
+        <v>71000</v>
+      </c>
+      <c r="AA9" s="3">
         <v>297200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>76000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>75000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>72000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>278400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>399000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>381600</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E10" s="3">
         <v>19000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>30000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>22900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>33000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>36000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>74000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>23000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>24000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>24000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>20300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>25000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>13000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>29000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>25000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>13000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>30000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>68500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>21000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>21000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>45900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>103000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>77700</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1317,65 +1337,68 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>-43500</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>-6000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-11000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>400</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-63000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-28800</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>20000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>72300</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>72300</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E17" s="3">
         <v>171000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>140000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>156100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>149000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>136000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>132000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>121200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>332000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>120000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>102000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>69000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>102000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>76000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>67000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>74400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>73000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>79000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>78000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>93300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>75000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>76000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>15000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>323400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>87000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>90000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>79000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>395200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>432000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>491100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-15000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>13600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>21000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>35500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>15000</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
       <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3">
         <v>22000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>29000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>19000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>19000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>8000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>86000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>42300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>14000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-70900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>70000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-31800</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,192 +1748,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-213000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-34000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>11000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-820200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>273000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>274000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>659000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>383100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>462000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>160000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>163000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>95900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>50000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>278000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-30700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-13000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-11000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-20000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-52800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-26000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-36000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>472000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-177900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-42000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-356000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-94000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-239100</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-153000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-17000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>33000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-812500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>302000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>274000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>687000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>411300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>526000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>161000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>189000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>142600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>74000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>285000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>32000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>24000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-53600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>566000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>42800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>27000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>18000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>20000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-254500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>24200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-228900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,192 +2031,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-181000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-40000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-831400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>287000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>259000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>673000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>396600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>483000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>145000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>176000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>131400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>65000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>278000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>25000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-15500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>16000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-61000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-7000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>558000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-135600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-426900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-24000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-270900</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>13000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>16000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>22300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-18000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-9000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3000</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>5000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>72800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4000</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>4000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>19000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-190000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-37000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-835300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>271000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>257000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>657000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>374300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>501000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>154000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>178000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>134700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>62000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>278000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>20000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-18200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-61500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>552000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-208400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-32000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-429200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-43000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-280000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-205000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-30000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-842300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>251000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>265000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>639000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>392300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>538000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>172000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>180000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>144600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>59000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>279000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>15000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-22000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-11000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-60200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-16000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>545000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-240000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-38000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-42000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-447100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-48000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2554,11 +2615,11 @@
       <c r="E29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>8</v>
@@ -2566,77 +2627,80 @@
       <c r="I29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="3">
         <v>500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>8000</v>
       </c>
-      <c r="P29" s="3" t="s">
+      <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-1300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>26000</v>
-      </c>
-      <c r="T29" s="3">
-        <v>-1000</v>
       </c>
       <c r="U29" s="3">
         <v>-1000</v>
       </c>
       <c r="V29" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="W29" s="3">
         <v>-1600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-4000</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>476600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>47000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>22000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>35200</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E32" s="3">
         <v>34000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-11000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>820200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-273000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-274000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-659000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-383100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-462000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-160000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-163000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-95900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-50000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-278000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>30700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>13000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>11000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>20000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>52800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>26000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>36000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-472000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>177900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>26000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>20000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>42000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>356000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>94000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>239100</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-205000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-30000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-842300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>251000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>265000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>639000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>392300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>538000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>172000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>180000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>145100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>67000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>279000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>15000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-23400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>28000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-12000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-61800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-20000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>545000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>236600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-23000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>9000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-411900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-48000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-205000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-30000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-842300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>251000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>265000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>639000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>392300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>538000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>172000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>180000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>145100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>67000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>279000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>15000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-23400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>28000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-12000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-61800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-20000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>545000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>236600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-23000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>9000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-411900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-48000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3438,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>633000</v>
+      </c>
+      <c r="E41" s="3">
         <v>590000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>750000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>535200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>550000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>837000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>714000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>475000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>723000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>310000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>455000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>286200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>432000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>398000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>111000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>147200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>210000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>138000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>161000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>131100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>275000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>429000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>455000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1417400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>498000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>366000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>328000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>326600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>451000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>301100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3453,183 +3543,189 @@
         <v>16000</v>
       </c>
       <c r="E42" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F42" s="3">
         <v>6000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>46000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>11000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>39000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>15000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>22000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>564200</v>
-      </c>
-      <c r="O42" s="3">
-        <v>16000</v>
       </c>
       <c r="P42" s="3">
         <v>16000</v>
       </c>
       <c r="Q42" s="3">
+        <v>16000</v>
+      </c>
+      <c r="R42" s="3">
         <v>22000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>33600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>72000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>78000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>51000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>49900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>28000</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
       <c r="Y42" s="3">
         <v>0</v>
       </c>
       <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
         <v>7100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>50000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>54000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>110000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>89500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>85000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>85300</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E43" s="3">
         <v>75000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>53000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>73900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>52000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>48000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>530000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>63000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>55000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>99000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>44000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>47900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>33000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>31000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>29000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>39300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>34000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>32000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>33000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>35500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>43000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>31000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>35000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>44400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>383000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>280000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>289000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>296000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>271000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>266300</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3703,431 +3799,446 @@
         <v>0</v>
       </c>
       <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="3">
         <v>83000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>82000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>89000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>91700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>87000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>281000</v>
+      </c>
+      <c r="E45" s="3">
         <v>317000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>518000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>406700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>422000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>403000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>43000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>44000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>48000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>220000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>29000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>21400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>20000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>19000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>131000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>109500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>147000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>116000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>100000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>111100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>21000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>18000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>20000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>35800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>40000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>102000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>53000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>49800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>62000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1010000</v>
+      </c>
+      <c r="E46" s="3">
         <v>998000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1327000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1061700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1034000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1299000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1291000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>582000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>865000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>644000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>550000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>919800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>501000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>464000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>293000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>329500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>463000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>364000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>345000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>327700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>367000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>478000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>510000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1504600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1054000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>884000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>869000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>853600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>956000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>809900</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>696000</v>
+      </c>
+      <c r="E47" s="3">
         <v>901000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>929000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1079400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1966000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1807000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1611000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1899000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1571000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1209000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1261000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>532400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>137000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>91000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>118000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>119700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>304000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>297000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>290000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>301200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>478000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>498000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>509000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>228400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>287000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>295000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>185000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>208200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>295000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>224800</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1771000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1784000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1581000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1321700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1243000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1215000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1257000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1224000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1099000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1044000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1018000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>904600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>804000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>784000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>684000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>684800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>681000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>670000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>659000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>635100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>627000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>609000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>628000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>616200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3503000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3507000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3553000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3497300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3524000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3487300</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>285000</v>
+      </c>
+      <c r="E49" s="3">
         <v>288000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>245000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>220800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>222000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>219000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>223000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>225000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>208000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>214000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>217000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1500</v>
-      </c>
-      <c r="O49" s="3">
-        <v>1000</v>
       </c>
       <c r="P49" s="3">
         <v>1000</v>
@@ -4136,10 +4247,10 @@
         <v>1000</v>
       </c>
       <c r="R49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S49" s="3">
         <v>1200</v>
-      </c>
-      <c r="S49" s="3">
-        <v>1000</v>
       </c>
       <c r="T49" s="3">
         <v>1000</v>
@@ -4148,10 +4259,10 @@
         <v>1000</v>
       </c>
       <c r="V49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W49" s="3">
         <v>1300</v>
-      </c>
-      <c r="W49" s="3">
-        <v>2000</v>
       </c>
       <c r="X49" s="3">
         <v>2000</v>
@@ -4160,28 +4271,31 @@
         <v>2000</v>
       </c>
       <c r="Z49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA49" s="3">
         <v>1600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>362000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>364000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>366000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>376800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>359000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>356200</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4481,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E52" s="3">
         <v>120000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>91000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>88400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>96000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>126000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>138000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>109000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>124000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>137000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>114000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>124100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>590000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>573000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>454000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>373100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>202000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>198000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>194000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>189800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>187000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>182000</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>175000</v>
       </c>
       <c r="Z52" s="3">
         <v>175000</v>
       </c>
       <c r="AA52" s="3">
+        <v>175000</v>
+      </c>
+      <c r="AB52" s="3">
         <v>153000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>161000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>212000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>201900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>129000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>176700</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3916000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4091000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4173000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3772100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4561000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4666000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4520000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4039000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3867000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3248000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3160000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2482300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2033000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1913000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1550000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1508400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1651000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1530000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1489000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1455100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1661000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1769000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1824000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2525900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5359000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5211000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5185000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5137800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5263000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5054900</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4838,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>231000</v>
+      </c>
+      <c r="E57" s="3">
         <v>222000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>206000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>133400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>122000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>108000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>126000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>342500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>138000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>136000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>154000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>128200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>68000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>54000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>34000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>36000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>62000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>61000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>58000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>47700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>65000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>49000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>42000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>58900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>260000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>226000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>289000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>285600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>336000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>283300</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E58" s="3">
         <v>89000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>82000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>39300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>54000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>51000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>41000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>38000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>429000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>50000</v>
       </c>
       <c r="M58" s="3">
         <v>50000</v>
       </c>
       <c r="N58" s="3">
+        <v>50000</v>
+      </c>
+      <c r="O58" s="3">
         <v>46500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>48000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>47000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>105000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>45600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>40000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>36000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>28000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>23200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>23000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>79000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>86000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>448000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>225000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>322000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>501000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>482800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>364000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E59" s="3">
         <v>18000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>169000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>574000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>426600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>45000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>34000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>28000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>53200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>33000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>27000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>25000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>23400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>36000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>28000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>19000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>17000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>106000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>125000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>299500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>179000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>213000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>251000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>276300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>343000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>332100</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>362000</v>
+      </c>
+      <c r="E60" s="3">
         <v>329000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>457000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>193000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>199000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>733000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>193000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>447000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>612000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>220000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>232000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>227900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>149000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>128000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>164000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>105000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>138000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>113000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>114000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>89900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>105000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>234000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>253000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>806300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>664000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>761000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1041000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1044800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1043000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>955200</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1252000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1268000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1203000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1123800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1101000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1117000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1192000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1172000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1094000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1042000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1001000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>871800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>714000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>688000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>555000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>576700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>586000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>582000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>575000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>563200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>585000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>564000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>584000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>588500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3344000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3170000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2892000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2829600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2941000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2820000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>235000</v>
+      </c>
+      <c r="E62" s="3">
         <v>225000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>193000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>159400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>151000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>177000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>174000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>168000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>151000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>156000</v>
       </c>
       <c r="M62" s="3">
         <v>156000</v>
       </c>
       <c r="N62" s="3">
+        <v>156000</v>
+      </c>
+      <c r="O62" s="3">
         <v>106600</v>
-      </c>
-      <c r="O62" s="3">
-        <v>124000</v>
       </c>
       <c r="P62" s="3">
         <v>124000</v>
       </c>
       <c r="Q62" s="3">
+        <v>124000</v>
+      </c>
+      <c r="R62" s="3">
         <v>121000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>114900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>109000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>102000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>99000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>86200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>88000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>84000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>85000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>79600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>360000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>375000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>363000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>369200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>345000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>336300</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2716000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2671000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2703000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2173600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2128000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2534000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2084000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2245000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2286000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1858000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1846000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1415500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1073000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1022000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>921000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>885000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>936000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>879000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>855000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>806100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>848000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>949000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>997000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1542700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4622000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4522000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4514000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4456600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4545000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4321100</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1158000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1375000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1421000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1547100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2384000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2079000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1814000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1166000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>960000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>770000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>699000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>448500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>360000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>293000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>92000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>42000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>33000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>45800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>207000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>229000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>258000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-282500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-531000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-575000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-584000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-564500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-533000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-513100</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1420000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1470000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1598500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2433000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2132000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2436000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1794000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1581000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1390000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1314000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1066800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>960000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>891000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>629000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>623400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>715000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>651000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>634000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>649000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>813000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>820000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>827000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>983100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>737000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>689000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>671000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>681200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>718000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>733800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-205000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-30000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-842300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>251000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>265000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>639000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>392300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>538000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>172000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>180000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>145100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>67000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>279000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>15000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-23400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>28000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-12000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-61800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-20000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>545000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>236600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-23000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>9000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-411900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-48000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7003,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E83" s="3">
         <v>23000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>18900</v>
-      </c>
-      <c r="G83" s="3">
-        <v>15000</v>
       </c>
       <c r="H83" s="3">
         <v>15000</v>
       </c>
       <c r="I83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="J83" s="3">
         <v>14000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>43000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>16000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>9000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>7000</v>
       </c>
       <c r="Q83" s="3">
         <v>7000</v>
       </c>
       <c r="R83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="S83" s="3">
         <v>9100</v>
-      </c>
-      <c r="S83" s="3">
-        <v>8000</v>
       </c>
       <c r="T83" s="3">
         <v>8000</v>
       </c>
       <c r="U83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="V83" s="3">
         <v>7000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>8000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>7000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>8000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>178500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>43000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>44000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>48000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>172400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>48200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>41900</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E89" s="3">
         <v>163000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>26000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>48400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>163000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>542000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>18000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>107500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>133000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>28000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>22000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>35000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>33000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>15000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>35000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>47000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>163400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>10000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>13000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-134000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>391900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>40000</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>101000</v>
       </c>
       <c r="AC89" s="3">
         <v>101000</v>
       </c>
       <c r="AD89" s="3">
+        <v>101000</v>
+      </c>
+      <c r="AE89" s="3">
         <v>162300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>65600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>52300</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7703,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-87000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-57000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-45300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-60000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-78000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-87000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-80700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-61000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-46000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-45000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-24500</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-11000</v>
       </c>
       <c r="P91" s="3">
         <v>-11000</v>
       </c>
       <c r="Q91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="R91" s="3">
         <v>-28000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-36300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-227600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-40000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-290600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-103300</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-241000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-31000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-70400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-80000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-430000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>377000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-61500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-144000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-52000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-98000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-327600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>211000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-89000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>50000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>3000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-46000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-197400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-115000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>217000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>584500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>3000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-62000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-114000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-399600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-36300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-167400</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7897,35 +8131,35 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-552000</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>-189000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-100000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-114100</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8496,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-78000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>220000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-369000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>21000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-150000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-304400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>451000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-129000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>254000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>162800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>13000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>44000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>36000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-109600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>31000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>13000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-8000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-108600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-50000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1049000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>97100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>90000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>3000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>174600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>119200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
+      <c r="D101" s="3">
+        <v>-7000</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3">
         <v>3400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-10000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-6000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>9700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>8000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>9600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>4000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>17300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>3000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>11000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>5400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-160000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>215000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-14400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-287000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>123000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>239000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-248600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>437000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-145000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>169000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-146000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>34000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>286000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-35000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-63000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>72000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-23000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>30000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-144300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-154000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-962000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1090800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>132000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>38000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-57300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>149900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-87500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>KEN</t>
   </si>
@@ -656,429 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>150800</v>
+      </c>
+      <c r="F8" s="3">
         <v>229000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>165000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>147000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>145000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>163000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>121000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>146000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>134800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>353000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>105000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>115000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>104500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>117000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>76000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>89000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>89500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>102000</v>
-      </c>
-      <c r="U8" s="3">
-        <v>85000</v>
-      </c>
-      <c r="V8" s="3">
-        <v>97000</v>
       </c>
       <c r="W8" s="3">
         <v>85000</v>
       </c>
       <c r="X8" s="3">
+        <v>97000</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>85000</v>
+      </c>
+      <c r="Z8" s="3">
         <v>94000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>84000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>101000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>365700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>97000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>84000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>93000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>324300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>502000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>459300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>133300</v>
+      </c>
+      <c r="F9" s="3">
         <v>176000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>146000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>117000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>122100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>130000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>113000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>110000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>110400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>279000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>93000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>92000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>90200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>93000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>66000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>65000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>69200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>77000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>72000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>68000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>78300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>69000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>71000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>71000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>297200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>76000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>75000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>72000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>278400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>399000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>381600</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>17500</v>
+      </c>
+      <c r="F10" s="3">
         <v>53000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>19000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>30000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>22900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>33000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>8000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>36000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>24400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>74000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>12000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>23000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>14300</v>
-      </c>
-      <c r="P10" s="3">
-        <v>24000</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>10000</v>
       </c>
       <c r="R10" s="3">
         <v>24000</v>
       </c>
       <c r="S10" s="3">
+        <v>10000</v>
+      </c>
+      <c r="T10" s="3">
+        <v>24000</v>
+      </c>
+      <c r="U10" s="3">
         <v>20300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>25000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>13000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>29000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>6700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>25000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>13000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>30000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>68500</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>21000</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>9000</v>
       </c>
       <c r="AD10" s="3">
         <v>21000</v>
       </c>
       <c r="AE10" s="3">
+        <v>9000</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>21000</v>
+      </c>
+      <c r="AG10" s="3">
         <v>45900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>103000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>77700</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,8 +1137,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1234,14 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,31 +1335,37 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1340,65 +1379,71 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>-43500</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="Q14" s="3">
+        <v>-43500</v>
+      </c>
+      <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>-6000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-11000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>400</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-63000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>-28800</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>20000</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>72300</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
       </c>
       <c r="AG14" s="3">
         <v>72300</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>72300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1537,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1575,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>142200</v>
+      </c>
+      <c r="F17" s="3">
         <v>197000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>171000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>140000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>156100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>149000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>136000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>132000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>121200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>332000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>120000</v>
-      </c>
-      <c r="N17" s="3">
-        <v>102000</v>
-      </c>
-      <c r="O17" s="3">
-        <v>69000</v>
       </c>
       <c r="P17" s="3">
         <v>102000</v>
       </c>
       <c r="Q17" s="3">
+        <v>69000</v>
+      </c>
+      <c r="R17" s="3">
+        <v>102000</v>
+      </c>
+      <c r="S17" s="3">
         <v>76000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>67000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>74400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>73000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>79000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>78000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>93300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>75000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>76000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>15000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>323400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>87000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>90000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>79000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>395200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>432000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>491100</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F18" s="3">
         <v>32000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-6000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>7000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-11100</v>
-      </c>
-      <c r="H18" s="3">
-        <v>14000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-15000</v>
       </c>
       <c r="J18" s="3">
         <v>14000</v>
       </c>
       <c r="K18" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>14000</v>
+      </c>
+      <c r="M18" s="3">
         <v>13600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>21000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-15000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>13000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>35500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>15000</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
         <v>22000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>15100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>29000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>6000</v>
-      </c>
-      <c r="V18" s="3">
-        <v>19000</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-8300</v>
       </c>
       <c r="X18" s="3">
         <v>19000</v>
       </c>
       <c r="Y18" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AA18" s="3">
         <v>8000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>86000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>42300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>10000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>14000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-70900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>70000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-31800</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,198 +1814,212 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-213000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-34000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>11000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-820200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>273000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>274000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>659000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>383100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>462000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>160000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>163000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>95900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>50000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>278000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>3000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-30700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-13000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-11000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-20000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-52800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-36000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>472000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-177900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-42000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-356000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-94000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-239100</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>43200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-153000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-17000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>33000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-812500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>302000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>274000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>687000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>411300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>526000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>161000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>189000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>142600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>74000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>285000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>32000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-6400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>24000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>3000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>6000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-53600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>566000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>42800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>27000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>18000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>20000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-254500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>24200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-228900</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2034,198 +2113,216 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>18300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-181000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-40000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>18000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-831400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>287000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>259000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>673000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>396600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>483000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>145000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>176000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>131400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>65000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>278000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>25000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-15500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>16000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-5000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-1000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-61000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>558000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-135600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-26000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-28000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-426900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-24000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-270900</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F24" s="3">
         <v>9000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-3000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>13000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>4000</v>
-      </c>
-      <c r="H24" s="3">
-        <v>16000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>2000</v>
       </c>
       <c r="J24" s="3">
         <v>16000</v>
       </c>
       <c r="K24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L24" s="3">
+        <v>16000</v>
+      </c>
+      <c r="M24" s="3">
         <v>22300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-18000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-9000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-2000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-3300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>3000</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>5000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>2700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>7000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>5000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>4000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>1000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>6000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>72800</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>4000</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>0</v>
       </c>
       <c r="AD24" s="3">
         <v>4000</v>
       </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AG24" s="3">
         <v>2300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>19000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2416,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-190000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-37000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>5000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-835300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>271000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>257000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>657000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>374300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>501000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>154000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>178000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>134700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>62000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>278000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>20000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-18200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>9000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-7000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-6000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-61500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-29000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>552000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-208400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-26000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-32000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-429200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-43000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-280000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-205000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-30000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-8000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-842300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>251000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>265000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>639000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>392300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>538000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>172000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>180000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>144600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>59000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>279000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>15000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-22000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>2000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-7000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-11000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-60200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-29000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>545000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-240000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-38000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-42000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-447100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-48000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,103 +2719,115 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3" t="s">
+      <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="Q29" s="3">
+        <v>500</v>
+      </c>
+      <c r="R29" s="3">
+        <v>8000</v>
+      </c>
+      <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="V29" s="3">
+        <v>26000</v>
+      </c>
+      <c r="W29" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="X29" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>476600</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>47000</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>22000</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>35200</v>
+      </c>
+      <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3" t="s">
+      <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O29" s="3">
-        <v>500</v>
-      </c>
-      <c r="P29" s="3">
-        <v>8000</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="T29" s="3">
-        <v>26000</v>
-      </c>
-      <c r="U29" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="V29" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="W29" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="X29" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>476600</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>47000</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>22000</v>
-      </c>
-      <c r="AE29" s="3">
-        <v>35200</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +3022,216 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="F32" s="3">
         <v>213000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>34000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-11000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>820200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-273000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-274000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-659000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-383100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-462000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-160000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-163000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-95900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-50000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-278000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-3000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>30700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>13000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>11000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>20000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>52800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>26000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>36000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-472000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>177900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>26000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>20000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>42000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>356000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>94000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>239100</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-205000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-30000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-8000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-842300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>251000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>265000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>639000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>392300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>538000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>172000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>180000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>145100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>67000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>279000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>15000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-23400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>28000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-8000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-12000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-61800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-29000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>545000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>236600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-23000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>9000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-411900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-48000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3325,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-205000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-30000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-8000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-842300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>251000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>265000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>639000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>392300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>538000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>172000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>180000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>145100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>67000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>279000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>15000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-23400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>28000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-8000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-12000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-61800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-29000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>545000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>236600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-23000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>9000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-411900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-48000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,293 +3610,313 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>677000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>696800</v>
+      </c>
+      <c r="F41" s="3">
         <v>633000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>590000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>750000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>535200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>550000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>837000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>714000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>475000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>723000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>310000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>455000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>286200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>432000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>398000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>111000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>147200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>210000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>138000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>161000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>131100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>275000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>429000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>455000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1417400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>498000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>366000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>328000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>326600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>451000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>301100</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>193000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>216300</v>
+      </c>
+      <c r="F42" s="3">
+        <v>252000</v>
+      </c>
+      <c r="G42" s="3">
+        <v>279000</v>
+      </c>
+      <c r="H42" s="3">
+        <v>315000</v>
+      </c>
+      <c r="I42" s="3">
+        <v>390800</v>
+      </c>
+      <c r="J42" s="3">
+        <v>368000</v>
+      </c>
+      <c r="K42" s="3">
+        <v>11000</v>
+      </c>
+      <c r="L42" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>39000</v>
+      </c>
+      <c r="O42" s="3">
+        <v>15000</v>
+      </c>
+      <c r="P42" s="3">
+        <v>22000</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>564200</v>
+      </c>
+      <c r="R42" s="3">
         <v>16000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="S42" s="3">
         <v>16000</v>
       </c>
-      <c r="F42" s="3">
-        <v>6000</v>
-      </c>
-      <c r="G42" s="3">
-        <v>46000</v>
-      </c>
-      <c r="H42" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I42" s="3">
-        <v>11000</v>
-      </c>
-      <c r="J42" s="3">
-        <v>4000</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>39000</v>
-      </c>
-      <c r="M42" s="3">
-        <v>15000</v>
-      </c>
-      <c r="N42" s="3">
+      <c r="T42" s="3">
         <v>22000</v>
       </c>
-      <c r="O42" s="3">
-        <v>564200</v>
-      </c>
-      <c r="P42" s="3">
-        <v>16000</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R42" s="3">
-        <v>22000</v>
-      </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>33600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>72000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>78000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>51000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>49900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>28000</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="3">
-        <v>0</v>
-      </c>
       <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
         <v>7100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>50000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>54000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>110000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>89500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>85000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>85300</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>68000</v>
+      </c>
+      <c r="F43" s="3">
         <v>80000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>75000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>53000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>73900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>52000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>48000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>530000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>63000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>55000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>99000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>44000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>47900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>33000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>31000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>29000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>39300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>34000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>32000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>33000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>35500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>43000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>31000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>35000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>44400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>383000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>280000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>289000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>296000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>271000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>266300</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3802,500 +3993,536 @@
         <v>0</v>
       </c>
       <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="3">
         <v>83000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>82000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>89000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>91700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>87000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>281000</v>
+        <v>106000</v>
       </c>
       <c r="E45" s="3">
-        <v>317000</v>
+        <v>114900</v>
       </c>
       <c r="F45" s="3">
-        <v>518000</v>
+        <v>45000</v>
       </c>
       <c r="G45" s="3">
-        <v>406700</v>
+        <v>54000</v>
       </c>
       <c r="H45" s="3">
-        <v>422000</v>
+        <v>209000</v>
       </c>
       <c r="I45" s="3">
+        <v>61900</v>
+      </c>
+      <c r="J45" s="3">
+        <v>64000</v>
+      </c>
+      <c r="K45" s="3">
         <v>403000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>43000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>44000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>48000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>220000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>29000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>21400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>20000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>19000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>131000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>109500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>147000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>116000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>100000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>111100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>21000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>18000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>20000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>35800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>40000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>102000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>53000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>49800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>62000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1043000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1096000</v>
+      </c>
+      <c r="F46" s="3">
         <v>1010000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>998000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1327000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1061700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1034000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1299000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1291000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>582000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>865000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>644000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>550000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>919800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>501000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>464000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>293000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>329500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>463000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>364000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>345000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>327700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>367000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>478000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>510000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1504600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1054000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>884000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>869000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>853600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>956000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>809900</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>700000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>703200</v>
+      </c>
+      <c r="F47" s="3">
         <v>696000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>901000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>929000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1079400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>1966000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1807000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1611000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1899000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1571000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1209000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1261000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>532400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>137000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>91000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>118000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>119700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>304000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>297000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>290000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>301200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>478000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>498000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>509000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>228400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>287000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>295000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>185000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>208200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>295000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>224800</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1902000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1889300</v>
+      </c>
+      <c r="F48" s="3">
         <v>1771000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1784000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1581000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1321700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1243000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1215000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1257000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1224000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1099000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1044000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1018000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>904600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>804000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>784000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>684000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>684800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>681000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>670000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>659000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>635100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>627000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>609000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>628000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>616200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>3503000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>3507000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>3553000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>3497300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>3524000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>3487300</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>311000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>321300</v>
+      </c>
+      <c r="F49" s="3">
         <v>285000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>288000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>245000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>220800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>222000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>219000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>223000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>225000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>208000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>214000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>217000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1500</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>1000</v>
       </c>
       <c r="R49" s="3">
         <v>1000</v>
       </c>
       <c r="S49" s="3">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="T49" s="3">
         <v>1000</v>
       </c>
       <c r="U49" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="V49" s="3">
         <v>1000</v>
       </c>
       <c r="W49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y49" s="3">
         <v>1300</v>
-      </c>
-      <c r="X49" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>2000</v>
       </c>
       <c r="Z49" s="3">
         <v>2000</v>
       </c>
       <c r="AA49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AC49" s="3">
         <v>1600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>362000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>364000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>366000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>376800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>359000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>356200</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4717,115 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>98600</v>
+      </c>
+      <c r="F52" s="3">
         <v>154000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>120000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>91000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>88400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>96000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>126000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>138000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>109000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>124000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>137000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>114000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>124100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>590000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>573000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>454000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>373100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>202000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>198000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>194000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>189800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>187000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>182000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>175000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>175000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>153000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>161000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>212000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>201900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>129000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>176700</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4919,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4053000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4108400</v>
+      </c>
+      <c r="F54" s="3">
         <v>3916000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4091000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>4173000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>3772100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>4561000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>4666000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>4520000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>4039000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>3867000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3248000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3160000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2482300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2033000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1913000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1550000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1508400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1651000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1530000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1489000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1455100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1661000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1769000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1824000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>2525900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>5359000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>5211000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>5185000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>5137800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>5263000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>5054900</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,578 +5098,616 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>181900</v>
+      </c>
+      <c r="F57" s="3">
         <v>231000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>222000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>206000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>133400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>122000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>108000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>126000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>342500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>138000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>136000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>154000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>128200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>68000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>54000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>34000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>36000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>62000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>61000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>58000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>47700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>65000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>49000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>42000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>58900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>260000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>226000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>289000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>285600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>336000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>283300</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>169600</v>
+      </c>
+      <c r="F58" s="3">
         <v>114000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>89000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>82000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>39300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>54000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>51000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>41000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>38000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>429000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>50000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>50000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>46500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>48000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>47000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>105000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>45600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>40000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>36000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>28000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>23200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>23000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>79000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>86000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>448000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>225000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>322000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>501000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>482800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>364000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F59" s="3">
         <v>17000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>18000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>169000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>20300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>23000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>574000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>26000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>426600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>45000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>34000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>28000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>53200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>33000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>27000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>25000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>23400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>36000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>16000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>28000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>19000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>17000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>106000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>125000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>299500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>179000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>213000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>251000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>276300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>343000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>332100</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>496000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>358800</v>
+      </c>
+      <c r="F60" s="3">
         <v>362000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>329000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>457000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>193000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>199000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>733000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>193000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>447000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>612000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>220000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>232000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>227900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>149000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>128000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>164000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>105000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>138000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>113000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>114000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>89900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>105000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>234000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>253000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>806300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>664000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>761000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>1041000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>1044800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>1043000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>955200</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1381000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1360400</v>
+      </c>
+      <c r="F61" s="3">
         <v>1252000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1268000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1203000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1123800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1101000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1117000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1192000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1172000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1094000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1042000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1001000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>871800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>714000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>688000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>555000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>576700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>586000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>582000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>575000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>563200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>585000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>564000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>584000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>588500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>3344000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>3170000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>2892000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>2829600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>2941000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>2820000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>313000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>319000</v>
+      </c>
+      <c r="F62" s="3">
         <v>235000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>225000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>193000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>159400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>151000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>177000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>174000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>168000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>151000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>156000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>156000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>106600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>124000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>124000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>121000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>114900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>109000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>102000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>99000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>86200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>88000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>84000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>85000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>79600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>360000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>375000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>363000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>369200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>345000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>336300</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +6003,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3047000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2905100</v>
+      </c>
+      <c r="F66" s="3">
         <v>2716000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2671000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2703000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2173600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2128000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2534000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2084000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2245000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2286000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1858000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1846000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1415500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1073000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1022000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>921000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>885000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>936000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>879000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>855000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>806100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>848000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>949000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>997000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1542700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>4622000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>4522000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>4514000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>4456600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>4545000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>4321100</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6545,115 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>961000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1156800</v>
+      </c>
+      <c r="F72" s="3">
         <v>1158000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1375000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1421000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1547100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2384000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2079000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1814000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1166000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>960000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>770000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>699000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>448500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>360000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>293000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>11000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>3000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>92000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>42000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>33000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>45800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>207000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>229000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>258000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-282500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-531000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-575000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-584000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-564500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-533000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-513100</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6949,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1006000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1203300</v>
+      </c>
+      <c r="F76" s="3">
         <v>1200000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1420000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1470000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1598500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2433000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2132000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2436000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1794000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1581000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1390000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1314000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1066800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>960000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>891000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>629000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>623400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>715000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>651000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>634000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>649000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>813000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>820000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>827000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>983100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>737000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>689000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>671000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>681200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>718000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>733800</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +7151,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-205000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-30000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-8000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-842300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>251000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>265000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>639000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>392300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>538000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>172000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>180000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>145100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>67000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>279000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>15000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-23400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>28000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-8000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-12000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-61800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-29000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>545000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>236600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-23000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>9000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-411900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-48000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,103 +7399,111 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>24900</v>
+      </c>
+      <c r="F83" s="3">
         <v>28000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>23000</v>
-      </c>
-      <c r="F83" s="3">
-        <v>15000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>18900</v>
       </c>
       <c r="H83" s="3">
         <v>15000</v>
       </c>
       <c r="I83" s="3">
+        <v>18900</v>
+      </c>
+      <c r="J83" s="3">
         <v>15000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L83" s="3">
         <v>14000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>14600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>43000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>16000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>13000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>11200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>9000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>7000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>7000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>9100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>8000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>8000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>7000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>7400</v>
-      </c>
-      <c r="X83" s="3">
-        <v>8000</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>7000</v>
       </c>
       <c r="Z83" s="3">
         <v>8000</v>
       </c>
       <c r="AA83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="AC83" s="3">
         <v>178500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>43000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>44000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>48000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>172400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>48200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>41900</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +8001,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F89" s="3">
         <v>76000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>163000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>26000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>48400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>163000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>542000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>18000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>107500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>133000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>28000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>22000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>9200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>35000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>33000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>15000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-4600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>35000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>8000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>47000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>163400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>10000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>13000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-134000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>391900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>40000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>101000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>101000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>162300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>65600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>52300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,103 +8143,111 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-126100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-62000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-87000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-57000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-45300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-60000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-78000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-87000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-80700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-61000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-46000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-45000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-24500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-11000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-28000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-10100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-5000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-11000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-8000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-36300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-227600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-40000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-290600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-103300</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8442,115 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-118200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-42000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-241000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-31000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-70400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-80000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-430000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>377000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-61500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-144000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-52000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-98000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-327600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>211000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-89000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>50000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>3000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-46000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-12000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-197400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-115000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-18000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>217000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>584500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>3000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-62000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-114000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-399600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-36300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-167400</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8584,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8128,44 +8595,44 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>-552000</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-189000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-100000</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-114100</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -8214,8 +8681,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,289 +8984,313 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>166600</v>
+      </c>
+      <c r="F100" s="3">
         <v>16000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-78000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>220000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>4300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-369000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>21000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-150000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-304400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>451000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-129000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>254000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>162800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>13000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>44000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>36000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-109600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>31000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>13000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-8000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-108600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-50000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-1049000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>97100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>90000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>3000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>174600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>119200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-7000</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="G101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="H101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>3400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-10000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-6000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>9700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>8000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-9000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>9600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-2000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>3000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>1300</v>
       </c>
       <c r="T101" s="3">
         <v>3000</v>
       </c>
       <c r="U101" s="3">
-        <v>2000</v>
+        <v>1300</v>
       </c>
       <c r="V101" s="3">
         <v>3000</v>
       </c>
       <c r="W101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-1700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>4000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>17300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>3000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>11000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>5400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>1300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>63700</v>
+      </c>
+      <c r="F102" s="3">
         <v>43000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-160000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>215000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-14400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-287000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>123000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>239000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-248600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>437000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-145000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>169000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-146000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>34000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>286000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-35000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-63000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>72000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-23000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>30000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-144300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-154000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-26000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-962000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>1090800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>132000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>38000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>1000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-57300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>149900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-87500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>KEN</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>181000</v>
+      </c>
+      <c r="E8" s="3">
         <v>174000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>150800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>229000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>165000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>147000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>145000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>163000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>121000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>146000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>134800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>353000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>105000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>115000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>104500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>117000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>76000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>89000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>89500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>102000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>85000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>97000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>85000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>94000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>84000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>101000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>365700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>97000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>84000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>93000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>324300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>502000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>459300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E9" s="3">
         <v>137000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>133300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>176000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>146000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>117000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>122100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>130000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>113000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>110000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>110400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>279000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>93000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>92000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>90200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>93000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>66000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>65000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>69200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>77000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>72000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>68000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>78300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>69000</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>71000</v>
       </c>
       <c r="AB9" s="3">
         <v>71000</v>
       </c>
       <c r="AC9" s="3">
+        <v>71000</v>
+      </c>
+      <c r="AD9" s="3">
         <v>297200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>76000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>75000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>72000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>278400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>399000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>381600</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E10" s="3">
         <v>37000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>17500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>53000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>30000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>33000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>36000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>74000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>23000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>14300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>24000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>24000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>20300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>25000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>13000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>29000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>25000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>13000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>30000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>68500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>21000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>9000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>21000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>45900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>103000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>77700</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,8 +1358,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1367,8 +1387,8 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1385,65 +1405,68 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>-43500</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>-6000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-11000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>400</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-63000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-28800</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>20000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>72300</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>72300</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>172000</v>
+      </c>
+      <c r="E17" s="3">
         <v>168000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>142200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>197000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>171000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>140000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>156100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>149000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>136000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>132000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>121200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>332000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>120000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>102000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>69000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>102000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>76000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>67000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>74400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>73000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>79000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>78000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>93300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>75000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>76000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>15000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>323400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>87000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>90000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>79000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>395200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>432000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>491100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E18" s="3">
         <v>6000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>8600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>32000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>21000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>35500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15000</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
       <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
         <v>22000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>15100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>29000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>19000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>19000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>8000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>86000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>42300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>14000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-70900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>70000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-31800</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,210 +1849,217 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E20" s="3">
         <v>11000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>9700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-213000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-34000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>11000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-820200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>273000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>274000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>659000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>383100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>462000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>160000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>163000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>95900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>50000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>278000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-30700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-13000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-11000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-52800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-36000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>472000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-177900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-42000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-356000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-94000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-239100</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E21" s="3">
         <v>39000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>43200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-153000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-17000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>33000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-812500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>302000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>274000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>687000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>411300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>526000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>161000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>189000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>142600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>74000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>285000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>32000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-6400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>24000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-53600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-21000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>566000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>42800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>27000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>18000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>20000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-254500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>24200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-228900</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2119,210 +2159,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E23" s="3">
         <v>17000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-181000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-40000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>18000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-831400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>287000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>259000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>673000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>396600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>483000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>145000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>176000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>131400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>65000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>278000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>25000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-15500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>16000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-61000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>558000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-135600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-28000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-426900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-24000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-270900</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>7000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>13000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>16000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>16000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>22300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-18000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-9000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3000</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>5000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>72800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4000</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>4000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>19000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E26" s="3">
         <v>10000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-190000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-37000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-835300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>271000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>257000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>657000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>374300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>501000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>154000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>178000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>134700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>62000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>278000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>20000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-18200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-61500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-29000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>552000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-208400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-32000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-429200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-43000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-280000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E27" s="3">
         <v>8000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-205000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-30000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-842300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>251000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>265000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>639000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>392300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>538000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>172000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>180000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>144600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>59000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>279000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>15000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-22000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-60200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-29000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>545000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-240000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-38000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-42000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-447100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-48000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2751,83 +2812,86 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3">
         <v>500</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>8000</v>
       </c>
-      <c r="S29" s="3" t="s">
+      <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-1300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>26000</v>
-      </c>
-      <c r="W29" s="3">
-        <v>-1000</v>
       </c>
       <c r="X29" s="3">
         <v>-1000</v>
       </c>
       <c r="Y29" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>476600</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>47000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>22000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>35200</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-98000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-11000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-9700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>213000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>34000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-11000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>820200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-273000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-274000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-659000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-383100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-462000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-160000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-163000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-95900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-50000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-278000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>30700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>13000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>11000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>20000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>52800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>26000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>36000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-472000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>177900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>26000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>20000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>42000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>356000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>94000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>239100</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E33" s="3">
         <v>8000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-205000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-30000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-842300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>251000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>265000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>639000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>392300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>538000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>172000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>180000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>145100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>67000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>279000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>15000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-23400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>28000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-61800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-29000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>545000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>236600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-23000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>9000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-411900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-48000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E35" s="3">
         <v>8000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-205000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-30000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-842300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>251000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>265000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>639000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>392300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>538000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>172000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>180000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>145100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>67000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>279000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>15000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-23400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>28000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-61800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-29000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>545000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>236600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-23000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>9000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-411900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-48000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,311 +3698,321 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>586000</v>
+      </c>
+      <c r="E41" s="3">
         <v>677000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>696800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>633000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>590000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>750000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>535200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>550000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>837000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>714000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>475000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>723000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>310000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>455000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>286200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>432000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>398000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>111000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>147200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>210000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>138000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>161000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>131100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>275000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>429000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>455000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1417400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>498000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>366000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>328000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>326600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>451000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>301100</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E42" s="3">
         <v>193000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>216300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>252000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>279000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>315000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>390800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>368000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>39000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>15000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>22000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>564200</v>
-      </c>
-      <c r="R42" s="3">
-        <v>16000</v>
       </c>
       <c r="S42" s="3">
         <v>16000</v>
       </c>
       <c r="T42" s="3">
+        <v>16000</v>
+      </c>
+      <c r="U42" s="3">
         <v>22000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>33600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>72000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>78000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>51000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>49900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>28000</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
-      </c>
       <c r="AB42" s="3">
         <v>0</v>
       </c>
       <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
         <v>7100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>50000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>54000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>110000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>89500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>85000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>85300</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E43" s="3">
         <v>67000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>68000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>80000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>75000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>53000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>73900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>52000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>48000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>530000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>63000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>55000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>99000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>44000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>47900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>33000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>31000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>29000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>39300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>34000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>32000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>33000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>35500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>43000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>31000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>35000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>44400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>383000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>280000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>289000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>296000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>271000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>266300</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3999,429 +4095,444 @@
         <v>0</v>
       </c>
       <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="3">
         <v>83000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>82000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>89000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>91700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>87000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E45" s="3">
         <v>106000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>114900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>45000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>54000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>209000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>61900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>64000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>403000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>43000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>44000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>48000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>220000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>29000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>21400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>20000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>19000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>131000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>109500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>147000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>116000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>100000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>111100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>21000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>18000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>20000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>35800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>40000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>102000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>53000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>49800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>62000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>948000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1043000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1096000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1010000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>998000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1327000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1061700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1034000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1299000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1291000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>582000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>865000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>644000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>550000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>919800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>501000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>464000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>293000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>329500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>463000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>364000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>345000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>327700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>367000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>478000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>510000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1504600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1054000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>884000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>869000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>853600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>956000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>809900</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>708000</v>
+      </c>
+      <c r="E47" s="3">
         <v>700000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>703200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>696000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>901000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>929000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1079400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1966000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1807000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1611000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1899000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1571000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1209000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1261000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>532400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>137000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>91000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>118000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>119700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>304000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>297000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>290000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>301200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>478000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>498000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>509000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>228400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>287000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>295000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>185000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>208200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>295000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>224800</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1937000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1902000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1889300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1771000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1784000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1581000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1321700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1243000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1215000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1257000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1224000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1099000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1044000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1018000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>904600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>804000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>784000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>684000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>684800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>681000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>670000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>659000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>635100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>627000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>609000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>628000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>616200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3503000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3507000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3553000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3497300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3524000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3487300</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4429,46 +4540,46 @@
         <v>311000</v>
       </c>
       <c r="E49" s="3">
+        <v>311000</v>
+      </c>
+      <c r="F49" s="3">
         <v>321300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>285000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>288000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>245000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>220800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>222000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>219000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>223000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>225000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>208000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>214000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>217000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1500</v>
-      </c>
-      <c r="R49" s="3">
-        <v>1000</v>
       </c>
       <c r="S49" s="3">
         <v>1000</v>
@@ -4477,10 +4588,10 @@
         <v>1000</v>
       </c>
       <c r="U49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V49" s="3">
         <v>1200</v>
-      </c>
-      <c r="V49" s="3">
-        <v>1000</v>
       </c>
       <c r="W49" s="3">
         <v>1000</v>
@@ -4489,10 +4600,10 @@
         <v>1000</v>
       </c>
       <c r="Y49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z49" s="3">
         <v>1300</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>2000</v>
       </c>
       <c r="AA49" s="3">
         <v>2000</v>
@@ -4501,28 +4612,31 @@
         <v>2000</v>
       </c>
       <c r="AC49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AD49" s="3">
         <v>1600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>362000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>364000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>366000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>376800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>359000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>356200</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E52" s="3">
         <v>97000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>98600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>154000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>120000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>91000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>88400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>96000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>126000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>138000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>109000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>124000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>137000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>114000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>124100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>590000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>573000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>454000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>373100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>202000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>198000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>194000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>189800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>187000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>182000</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>175000</v>
       </c>
       <c r="AC52" s="3">
         <v>175000</v>
       </c>
       <c r="AD52" s="3">
+        <v>175000</v>
+      </c>
+      <c r="AE52" s="3">
         <v>153000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>161000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>212000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>201900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>129000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>176700</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3994000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4053000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4108400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3916000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4091000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4173000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3772100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4561000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4666000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4520000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4039000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3867000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3248000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3160000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2482300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2033000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1913000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1550000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1508400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1651000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1530000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1489000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1455100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1661000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1769000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1824000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2525900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5359000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5211000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5185000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5137800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5263000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5054900</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E57" s="3">
         <v>179000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>181900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>231000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>222000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>206000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>133400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>122000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>108000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>126000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>342500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>138000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>136000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>154000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>128200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>68000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>54000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>34000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>36000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>62000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>61000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>58000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>47700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>65000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>49000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>42000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>58900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>260000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>226000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>289000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>285600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>336000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>283300</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E58" s="3">
         <v>107000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>169600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>114000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>89000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>82000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>39300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>54000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>51000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>41000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>38000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>429000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>50000</v>
       </c>
       <c r="P58" s="3">
         <v>50000</v>
       </c>
       <c r="Q58" s="3">
+        <v>50000</v>
+      </c>
+      <c r="R58" s="3">
         <v>46500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>48000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>47000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>105000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>45600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>40000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>36000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>28000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>23200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>23000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>79000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>86000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>448000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>225000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>322000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>501000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>482800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>364000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E59" s="3">
         <v>210000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>169000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>20300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>23000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>574000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>26000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>426600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>45000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>34000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>28000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>53200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>33000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>27000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>25000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>23400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>36000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>16000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>28000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>19000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>17000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>106000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>125000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>299500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>179000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>213000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>251000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>276300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>343000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>332100</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>308000</v>
+      </c>
+      <c r="E60" s="3">
         <v>496000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>358800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>362000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>329000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>457000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>193000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>199000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>733000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>193000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>447000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>612000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>220000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>232000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>227900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>149000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>128000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>164000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>105000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>138000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>113000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>114000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>89900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>105000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>234000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>253000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>806300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>664000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>761000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1041000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1044800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1043000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>955200</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1358000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1381000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1360400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1252000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1268000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1203000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1123800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1101000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1117000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1192000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1172000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1094000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1042000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1001000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>871800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>714000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>688000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>555000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>576700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>586000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>582000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>575000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>563200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>585000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>564000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>584000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>588500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3344000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3170000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2892000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2829600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2941000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2820000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>352000</v>
+      </c>
+      <c r="E62" s="3">
         <v>313000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>319000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>235000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>225000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>193000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>159400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>151000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>177000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>174000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>168000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>151000</v>
-      </c>
-      <c r="O62" s="3">
-        <v>156000</v>
       </c>
       <c r="P62" s="3">
         <v>156000</v>
       </c>
       <c r="Q62" s="3">
+        <v>156000</v>
+      </c>
+      <c r="R62" s="3">
         <v>106600</v>
-      </c>
-      <c r="R62" s="3">
-        <v>124000</v>
       </c>
       <c r="S62" s="3">
         <v>124000</v>
       </c>
       <c r="T62" s="3">
+        <v>124000</v>
+      </c>
+      <c r="U62" s="3">
         <v>121000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>114900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>109000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>102000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>99000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>86200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>88000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>84000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>85000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>79600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>360000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>375000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>363000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>369200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>345000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>336300</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2877000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3047000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2905100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2716000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2671000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2703000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2173600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2128000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2534000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2084000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2245000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2286000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1858000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1846000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1415500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1073000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1022000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>921000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>885000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>936000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>879000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>855000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>806100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>848000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>949000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>997000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1542700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4622000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4522000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4514000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4456600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4545000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4321100</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="E72" s="3">
         <v>961000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1156800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1158000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1375000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1421000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1547100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2384000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2079000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1814000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1166000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>960000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>770000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>699000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>448500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>360000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>293000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>92000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>42000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>33000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>45800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>207000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>229000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>258000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-282500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-531000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-575000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-584000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-564500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-533000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-513100</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1117000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1006000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1203300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1200000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1420000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1470000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1598500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2433000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2132000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2436000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1794000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1581000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1390000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1314000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1066800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>960000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>891000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>629000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>623400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>715000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>651000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>634000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>649000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>813000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>820000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>827000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>983100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>737000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>689000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>671000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>681200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>718000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>733800</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E81" s="3">
         <v>8000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-205000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-30000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-842300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>251000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>265000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>639000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>392300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>538000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>172000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>180000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>145100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>67000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>279000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>15000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-23400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>28000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-61800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-29000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>545000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>236600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-23000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>9000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-411900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-48000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E83" s="3">
         <v>22000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>24900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>28000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>23000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>15000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>18900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>15000</v>
       </c>
       <c r="K83" s="3">
         <v>15000</v>
       </c>
       <c r="L83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="M83" s="3">
         <v>14000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>43000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>16000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>11200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>9000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>7000</v>
       </c>
       <c r="T83" s="3">
         <v>7000</v>
       </c>
       <c r="U83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="V83" s="3">
         <v>9100</v>
-      </c>
-      <c r="V83" s="3">
-        <v>8000</v>
       </c>
       <c r="W83" s="3">
         <v>8000</v>
       </c>
       <c r="X83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Y83" s="3">
         <v>7000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>7400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>7000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>8000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>178500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>43000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>44000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>48000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>172400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>48200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>41900</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E89" s="3">
         <v>70000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>76000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>163000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>26000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>48400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>163000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>542000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>18000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>107500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>133000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>28000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>22000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>35000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>33000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>15000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>35000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>47000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>163400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>10000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>13000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-134000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>391900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>40000</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>101000</v>
       </c>
       <c r="AF89" s="3">
         <v>101000</v>
       </c>
       <c r="AG89" s="3">
+        <v>101000</v>
+      </c>
+      <c r="AH89" s="3">
         <v>162300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>65600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>52300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-68000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-69000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-126100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-62000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-87000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-57000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-45300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-60000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-78000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-87000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-80700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-61000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-46000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-45000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-24500</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-11000</v>
       </c>
       <c r="S91" s="3">
         <v>-11000</v>
       </c>
       <c r="T91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="U91" s="3">
         <v>-28000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-36300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-227600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-40000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-290600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-103300</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-35000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-118200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-42000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-241000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-31000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-70400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-80000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-430000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>377000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-61500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-144000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-52000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-98000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-327600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-16000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>211000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-89000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>50000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>3000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-46000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-197400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-115000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>217000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>584500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>3000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-62000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-114000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-399600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-36300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-167400</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8595,11 +8829,11 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>-400</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
@@ -8607,35 +8841,35 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-552000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-189000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-100000</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-114100</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-178000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-56000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>166600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>16000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-78000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>220000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-369000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>21000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-150000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-304400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>451000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-129000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>254000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>162800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>13000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>44000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>36000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-109600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>31000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>13000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-108600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-50000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1049000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>97100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>90000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>3000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>174600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>119200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7000</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3">
         <v>3400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-10000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-6000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>9700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>8000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>9600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>3000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>4000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>17300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>11000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>5400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-91000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-20000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>63700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>43000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-160000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>215000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-287000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>123000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>239000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-248600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>437000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-145000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>169000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-146000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>34000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>286000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-35000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-63000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>72000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-23000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>30000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-144300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-154000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-26000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-962000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1090800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>132000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>38000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-57300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>149900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-87500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
   <si>
     <t>KEN</t>
   </si>
@@ -913,25 +913,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>129000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>117000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>112300</v>
+      </c>
+      <c r="G9" s="3">
         <v>151000</v>
       </c>
-      <c r="E9" s="3">
-        <v>137000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>133300</v>
-      </c>
-      <c r="G9" s="3">
-        <v>176000</v>
-      </c>
       <c r="H9" s="3">
-        <v>146000</v>
+        <v>129000</v>
       </c>
       <c r="I9" s="3">
-        <v>117000</v>
+        <v>103000</v>
       </c>
       <c r="J9" s="3">
-        <v>122100</v>
+        <v>104300</v>
       </c>
       <c r="K9" s="3">
         <v>130000</v>
@@ -1017,25 +1017,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>30000</v>
+        <v>52000</v>
       </c>
       <c r="E10" s="3">
-        <v>37000</v>
+        <v>57000</v>
       </c>
       <c r="F10" s="3">
-        <v>17500</v>
+        <v>38500</v>
       </c>
       <c r="G10" s="3">
-        <v>53000</v>
+        <v>78000</v>
       </c>
       <c r="H10" s="3">
-        <v>19000</v>
+        <v>36000</v>
       </c>
       <c r="I10" s="3">
-        <v>30000</v>
+        <v>44000</v>
       </c>
       <c r="J10" s="3">
-        <v>22900</v>
+        <v>40700</v>
       </c>
       <c r="K10" s="3">
         <v>33000</v>
@@ -1367,25 +1367,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+        <v>-111000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>930400</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1471,25 +1471,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>25200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>21100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>7000</v>
       </c>
       <c r="J18" s="3">
-        <v>-11100</v>
+        <v>-11200</v>
       </c>
       <c r="K18" s="3">
         <v>14000</v>
@@ -1856,25 +1856,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>98000</v>
+        <v>-4000</v>
       </c>
       <c r="E20" s="3">
-        <v>11000</v>
+        <v>-20000</v>
       </c>
       <c r="F20" s="3">
-        <v>9700</v>
+        <v>-5300</v>
       </c>
       <c r="G20" s="3">
-        <v>-213000</v>
+        <v>201000</v>
       </c>
       <c r="H20" s="3">
-        <v>-34000</v>
+        <v>27000</v>
       </c>
       <c r="I20" s="3">
-        <v>11000</v>
+        <v>-12000</v>
       </c>
       <c r="J20" s="3">
-        <v>-820200</v>
+        <v>-144700</v>
       </c>
       <c r="K20" s="3">
         <v>273000</v>
@@ -1960,25 +1960,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>131000</v>
+        <v>35000</v>
       </c>
       <c r="E21" s="3">
-        <v>39000</v>
+        <v>46000</v>
       </c>
       <c r="F21" s="3">
-        <v>43200</v>
+        <v>39100</v>
       </c>
       <c r="G21" s="3">
-        <v>-153000</v>
+        <v>-144000</v>
       </c>
       <c r="H21" s="3">
-        <v>-17000</v>
+        <v>-16000</v>
       </c>
       <c r="I21" s="3">
         <v>33000</v>
       </c>
       <c r="J21" s="3">
-        <v>-812500</v>
+        <v>154600</v>
       </c>
       <c r="K21" s="3">
         <v>302000</v>
@@ -2064,25 +2064,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>-2700</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2271,8 +2271,8 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E24" s="3">
         <v>7000</v>
@@ -3104,25 +3104,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-98000</v>
+        <v>4000</v>
       </c>
       <c r="E32" s="3">
-        <v>-11000</v>
+        <v>20000</v>
       </c>
       <c r="F32" s="3">
-        <v>-9700</v>
+        <v>5300</v>
       </c>
       <c r="G32" s="3">
-        <v>213000</v>
+        <v>-201000</v>
       </c>
       <c r="H32" s="3">
-        <v>34000</v>
+        <v>-27000</v>
       </c>
       <c r="I32" s="3">
-        <v>-11000</v>
+        <v>12000</v>
       </c>
       <c r="J32" s="3">
-        <v>820200</v>
+        <v>144700</v>
       </c>
       <c r="K32" s="3">
         <v>-273000</v>
@@ -3815,7 +3815,7 @@
         <v>193000</v>
       </c>
       <c r="F42" s="3">
-        <v>216300</v>
+        <v>215800</v>
       </c>
       <c r="G42" s="3">
         <v>252000</v>
@@ -3827,7 +3827,7 @@
         <v>315000</v>
       </c>
       <c r="J42" s="3">
-        <v>390800</v>
+        <v>380400</v>
       </c>
       <c r="K42" s="3">
         <v>368000</v>
@@ -3919,7 +3919,7 @@
         <v>67000</v>
       </c>
       <c r="F43" s="3">
-        <v>68000</v>
+        <v>150800</v>
       </c>
       <c r="G43" s="3">
         <v>80000</v>
@@ -3931,7 +3931,7 @@
         <v>53000</v>
       </c>
       <c r="J43" s="3">
-        <v>73900</v>
+        <v>78600</v>
       </c>
       <c r="K43" s="3">
         <v>52000</v>
@@ -4016,26 +4016,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4127,7 +4127,7 @@
         <v>106000</v>
       </c>
       <c r="F45" s="3">
-        <v>114900</v>
+        <v>19200</v>
       </c>
       <c r="G45" s="3">
         <v>45000</v>
@@ -4139,7 +4139,7 @@
         <v>209000</v>
       </c>
       <c r="J45" s="3">
-        <v>61900</v>
+        <v>47200</v>
       </c>
       <c r="K45" s="3">
         <v>64000</v>
@@ -4451,7 +4451,7 @@
         <v>1581000</v>
       </c>
       <c r="J48" s="3">
-        <v>1321700</v>
+        <v>1349200</v>
       </c>
       <c r="K48" s="3">
         <v>1243000</v>
@@ -4849,25 +4849,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>90000</v>
+        <v>80000</v>
       </c>
       <c r="E52" s="3">
-        <v>97000</v>
+        <v>88000</v>
       </c>
       <c r="F52" s="3">
-        <v>98600</v>
+        <v>38500</v>
       </c>
       <c r="G52" s="3">
-        <v>154000</v>
+        <v>145000</v>
       </c>
       <c r="H52" s="3">
-        <v>120000</v>
+        <v>114000</v>
       </c>
       <c r="I52" s="3">
-        <v>91000</v>
+        <v>86000</v>
       </c>
       <c r="J52" s="3">
-        <v>88400</v>
+        <v>39800</v>
       </c>
       <c r="K52" s="3">
         <v>96000</v>
@@ -5243,7 +5243,7 @@
         <v>179000</v>
       </c>
       <c r="F57" s="3">
-        <v>181900</v>
+        <v>70700</v>
       </c>
       <c r="G57" s="3">
         <v>231000</v>
@@ -5255,7 +5255,7 @@
         <v>206000</v>
       </c>
       <c r="J57" s="3">
-        <v>133400</v>
+        <v>95000</v>
       </c>
       <c r="K57" s="3">
         <v>122000</v>
@@ -5341,25 +5341,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>101000</v>
+        <v>108000</v>
       </c>
       <c r="E58" s="3">
-        <v>107000</v>
+        <v>114000</v>
       </c>
       <c r="F58" s="3">
-        <v>169600</v>
+        <v>174600</v>
       </c>
       <c r="G58" s="3">
-        <v>114000</v>
+        <v>130000</v>
       </c>
       <c r="H58" s="3">
-        <v>89000</v>
+        <v>106000</v>
       </c>
       <c r="I58" s="3">
-        <v>82000</v>
+        <v>99000</v>
       </c>
       <c r="J58" s="3">
-        <v>39300</v>
+        <v>56700</v>
       </c>
       <c r="K58" s="3">
         <v>54000</v>
@@ -5445,25 +5445,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="E59" s="3">
-        <v>210000</v>
+        <v>203000</v>
       </c>
       <c r="F59" s="3">
-        <v>7300</v>
+        <v>10100</v>
       </c>
       <c r="G59" s="3">
-        <v>17000</v>
+        <v>1000</v>
       </c>
       <c r="H59" s="3">
-        <v>18000</v>
+        <v>1000</v>
       </c>
       <c r="I59" s="3">
-        <v>169000</v>
+        <v>152000</v>
       </c>
       <c r="J59" s="3">
-        <v>20300</v>
+        <v>9300</v>
       </c>
       <c r="K59" s="3">
         <v>23000</v>
@@ -5653,25 +5653,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1358000</v>
+        <v>1412000</v>
       </c>
       <c r="E61" s="3">
-        <v>1381000</v>
+        <v>1436000</v>
       </c>
       <c r="F61" s="3">
-        <v>1360400</v>
+        <v>1416900</v>
       </c>
       <c r="G61" s="3">
-        <v>1252000</v>
+        <v>1309000</v>
       </c>
       <c r="H61" s="3">
-        <v>1268000</v>
+        <v>1325000</v>
       </c>
       <c r="I61" s="3">
-        <v>1203000</v>
+        <v>1223000</v>
       </c>
       <c r="J61" s="3">
-        <v>1123800</v>
+        <v>1144000</v>
       </c>
       <c r="K61" s="3">
         <v>1101000</v>
@@ -5757,25 +5757,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>352000</v>
+        <v>168000</v>
       </c>
       <c r="E62" s="3">
-        <v>313000</v>
+        <v>126000</v>
       </c>
       <c r="F62" s="3">
-        <v>319000</v>
+        <v>125900</v>
       </c>
       <c r="G62" s="3">
-        <v>235000</v>
+        <v>41000</v>
       </c>
       <c r="H62" s="3">
-        <v>225000</v>
+        <v>39000</v>
       </c>
       <c r="I62" s="3">
-        <v>193000</v>
+        <v>43000</v>
       </c>
       <c r="J62" s="3">
-        <v>159400</v>
+        <v>41400</v>
       </c>
       <c r="K62" s="3">
         <v>151000</v>
@@ -6173,25 +6173,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2877000</v>
+        <v>2018000</v>
       </c>
       <c r="E66" s="3">
-        <v>3047000</v>
+        <v>2190000</v>
       </c>
       <c r="F66" s="3">
-        <v>2905100</v>
+        <v>2038200</v>
       </c>
       <c r="G66" s="3">
-        <v>2716000</v>
+        <v>1849000</v>
       </c>
       <c r="H66" s="3">
-        <v>2671000</v>
+        <v>1822000</v>
       </c>
       <c r="I66" s="3">
-        <v>2703000</v>
+        <v>1853000</v>
       </c>
       <c r="J66" s="3">
-        <v>2173600</v>
+        <v>1476100</v>
       </c>
       <c r="K66" s="3">
         <v>2128000</v>
@@ -6731,25 +6731,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1074000</v>
+        <v>1007000</v>
       </c>
       <c r="E72" s="3">
-        <v>961000</v>
+        <v>895000</v>
       </c>
       <c r="F72" s="3">
-        <v>1156800</v>
+        <v>1087000</v>
       </c>
       <c r="G72" s="3">
-        <v>1158000</v>
+        <v>1083000</v>
       </c>
       <c r="H72" s="3">
-        <v>1375000</v>
+        <v>1303000</v>
       </c>
       <c r="I72" s="3">
-        <v>1421000</v>
+        <v>1349000</v>
       </c>
       <c r="J72" s="3">
-        <v>1547100</v>
+        <v>1504600</v>
       </c>
       <c r="K72" s="3">
         <v>2384000</v>
@@ -7606,25 +7606,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="E83" s="3">
-        <v>22000</v>
+        <v>15000</v>
       </c>
       <c r="F83" s="3">
-        <v>24900</v>
+        <v>7300</v>
       </c>
       <c r="G83" s="3">
-        <v>28000</v>
+        <v>15000</v>
       </c>
       <c r="H83" s="3">
-        <v>23000</v>
+        <v>15000</v>
       </c>
       <c r="I83" s="3">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="J83" s="3">
-        <v>18900</v>
+        <v>3400</v>
       </c>
       <c r="K83" s="3">
         <v>15000</v>
@@ -8378,19 +8378,19 @@
         <v>-69000</v>
       </c>
       <c r="F91" s="3">
-        <v>-126100</v>
+        <v>-133100</v>
       </c>
       <c r="G91" s="3">
-        <v>-62000</v>
+        <v>-60000</v>
       </c>
       <c r="H91" s="3">
-        <v>-87000</v>
+        <v>-86000</v>
       </c>
       <c r="I91" s="3">
-        <v>-57000</v>
+        <v>-53000</v>
       </c>
       <c r="J91" s="3">
-        <v>-45300</v>
+        <v>-65300</v>
       </c>
       <c r="K91" s="3">
         <v>-60000</v>
@@ -8826,25 +8826,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+        <v>201000</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F96" s="3">
-        <v>-400</v>
+        <v>400</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>100</v>
+        <v>150000</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>-552000</v>
@@ -9346,25 +9346,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="E101" s="3">
-        <v>1000</v>
+        <v>-4000</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F101" s="3">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="G101" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>8</v>
+        <v>-1000</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-6000</v>
       </c>
       <c r="J101" s="3">
-        <v>3400</v>
+        <v>9700</v>
       </c>
       <c r="K101" s="3">
         <v>-1000</v>

--- a/AAII_Financials/Quarterly/KEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>KEN</t>
   </si>
@@ -656,467 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>237000</v>
+      </c>
+      <c r="E8" s="3">
         <v>181000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>174000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>150800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>229000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>165000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>147000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>145000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>163000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>121000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>146000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>134800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>353000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>105000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>115000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>104500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>117000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>76000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>89000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>89500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>102000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>85000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>97000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>85000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>94000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>84000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>101000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>365700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>97000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>84000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>93000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>324300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>502000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>459300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E9" s="3">
         <v>129000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>117000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>112300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>151000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>129000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>103000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>104300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>130000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>113000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>110000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>110400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>279000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>93000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>92000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>90200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>93000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>66000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>65000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>69200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>77000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>72000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>68000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>78300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>69000</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>71000</v>
       </c>
       <c r="AC9" s="3">
         <v>71000</v>
       </c>
       <c r="AD9" s="3">
+        <v>71000</v>
+      </c>
+      <c r="AE9" s="3">
         <v>297200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>76000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>75000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>72000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>278400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>399000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>381600</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E10" s="3">
         <v>52000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>57000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>38500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>78000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>36000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>44000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>40700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>33000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>36000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>24400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>74000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>12000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>23000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>14300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>24000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>24000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>20300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>25000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>13000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>29000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>25000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>13000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>30000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>68500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>21000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>9000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>21000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>45900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>103000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>77700</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1166,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1271,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,22 +1378,25 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-111000</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1384,14 +1404,14 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>930400</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1408,92 +1428,95 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>-43500</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>-6000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-11000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>400</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>-63000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-28800</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>20000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>72300</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>72300</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E15" s="3">
         <v>22000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>20000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>25200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>25000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>14000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1569,8 +1592,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1630,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E17" s="3">
         <v>172000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>168000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>142200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>197000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>171000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>140000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>156100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>149000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>136000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>132000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>121200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>332000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>120000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>102000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>69000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>102000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>76000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>67000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>74400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>73000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>79000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>78000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>93300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>75000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>76000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>15000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>323400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>87000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>90000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>79000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>395200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>432000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>491100</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E18" s="3">
         <v>9000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>32000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>21000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>35500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>15000</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>22000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>15100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>29000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>19000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>19000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>8000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>86000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>42300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>10000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>14000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-70900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>70000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-31800</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,243 +1883,250 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-20000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>201000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>27000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-12000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-144700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>273000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>274000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>659000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>383100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>462000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>160000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>163000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>95900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>50000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>278000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-30700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-13000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-52800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-36000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>472000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-177900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-42000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-356000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-94000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-239100</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E21" s="3">
         <v>35000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>46000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>39100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-144000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-16000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>33000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>154600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>302000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>274000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>687000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>411300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>526000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>161000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>189000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>142600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>74000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>285000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>32000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-6400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>24000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-53600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-21000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>566000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>42800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>27000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>18000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>20000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-254500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>24200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-228900</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E22" s="3">
         <v>31000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>21000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>-2700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>23000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>18000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8500</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -2162,216 +2202,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E23" s="3">
         <v>107000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>17000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-181000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-40000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>18000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-831400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>287000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>259000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>673000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>396600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>483000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>145000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>176000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>131400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>65000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>278000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>25000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-15500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>16000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-61000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-28000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>558000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-135600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-26000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-28000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-426900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-24000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-270900</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-3000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>13000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>16000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>16000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>22300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-18000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3000</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>5000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>72800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4000</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>4000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>19000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E26" s="3">
         <v>107000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-190000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-37000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-835300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>271000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>257000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>657000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>374300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>501000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>154000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>178000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>134700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>62000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>278000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>20000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-18200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>9000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-61500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-29000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>552000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-208400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-26000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-32000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-429200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-43000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-280000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E27" s="3">
         <v>112000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-205000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-30000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-842300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>251000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>265000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>639000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>392300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>538000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>172000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>180000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>144600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>59000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>279000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>15000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-22000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-60200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-29000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>545000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-240000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-38000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-42000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-447100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-48000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2815,83 +2876,86 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3">
         <v>500</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>8000</v>
       </c>
-      <c r="T29" s="3" t="s">
+      <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>-1300</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>26000</v>
-      </c>
-      <c r="X29" s="3">
-        <v>-1000</v>
       </c>
       <c r="Y29" s="3">
         <v>-1000</v>
       </c>
       <c r="Z29" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
         <v>0</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>476600</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>47000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>22000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>35200</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3165,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E32" s="3">
         <v>4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>20000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-201000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-27000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>12000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>144700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-273000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-274000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-659000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-383100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-462000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-160000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-163000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-95900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-50000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-278000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>30700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>13000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>11000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>20000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>52800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>26000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>36000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-472000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>177900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>26000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>20000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>42000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>356000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>94000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>239100</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E33" s="3">
         <v>112000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-205000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-30000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-842300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>251000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>265000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>639000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>392300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>538000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>172000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>180000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>145100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>67000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>279000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>15000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-23400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>28000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-61800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-29000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>545000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>236600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-23000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>9000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-411900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-48000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E35" s="3">
         <v>112000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-205000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-30000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-842300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>251000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>265000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>639000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>392300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>538000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>172000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>180000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>145100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>67000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>279000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>15000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-23400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>28000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-61800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-29000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>545000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>236600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-23000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>9000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-411900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-48000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,320 +3785,330 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>615000</v>
+      </c>
+      <c r="E41" s="3">
         <v>586000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>677000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>696800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>633000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>590000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>750000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>535200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>550000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>837000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>714000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>475000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>723000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>310000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>455000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>286200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>432000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>398000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>111000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>147200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>210000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>138000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>161000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>131100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>275000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>429000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>455000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1417400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>498000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>366000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>328000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>326600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>451000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>301100</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>158000</v>
+      </c>
+      <c r="E42" s="3">
         <v>165000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>193000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>215800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>252000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>279000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>315000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>380400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>368000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>39000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>15000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>22000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>564200</v>
-      </c>
-      <c r="S42" s="3">
-        <v>16000</v>
       </c>
       <c r="T42" s="3">
         <v>16000</v>
       </c>
       <c r="U42" s="3">
+        <v>16000</v>
+      </c>
+      <c r="V42" s="3">
         <v>22000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>33600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>72000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>78000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>51000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>49900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>28000</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
-      </c>
       <c r="AC42" s="3">
         <v>0</v>
       </c>
       <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
         <v>7100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>50000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>54000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>110000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>89500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>85000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>85300</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E43" s="3">
         <v>96000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>67000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>150800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>80000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>75000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>53000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>78600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>52000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>48000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>530000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>63000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>55000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>99000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>44000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>47900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>33000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>31000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>29000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>39300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>34000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>32000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>33000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>35500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>43000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>31000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>35000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>44400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>383000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>280000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>289000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>296000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>271000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>266300</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4133,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4098,491 +4194,506 @@
         <v>0</v>
       </c>
       <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="3">
         <v>83000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>82000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>89000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>91700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>87000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E45" s="3">
         <v>101000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>106000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>19200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>45000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>54000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>209000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>47200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>64000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>403000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>43000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>44000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>48000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>220000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>29000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>21400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>20000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>19000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>131000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>109500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>147000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>116000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>100000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>111100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>21000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>18000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>20000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>35800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>40000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>102000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>53000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>49800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>62000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>911000</v>
+      </c>
+      <c r="E46" s="3">
         <v>948000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1043000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1096000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1010000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>998000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1327000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1061700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1034000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1299000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1291000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>582000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>865000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>644000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>550000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>919800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>501000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>464000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>293000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>329500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>463000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>364000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>345000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>327700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>367000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>478000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>510000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1504600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1054000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>884000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>869000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>853600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>956000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>809900</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>693000</v>
+      </c>
+      <c r="E47" s="3">
         <v>708000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>700000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>703200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>696000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>901000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>929000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1079400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1966000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1807000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1611000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1899000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1571000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1209000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1261000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>532400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>137000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>91000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>118000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>119700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>304000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>297000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>290000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>301200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>478000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>498000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>509000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>228400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>287000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>295000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>185000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>208200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>295000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>224800</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2108000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1937000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1902000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1889300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1771000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1784000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1581000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1349200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1243000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1215000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1257000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1224000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1099000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1044000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1018000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>904600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>804000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>784000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>684000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>684800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>681000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>670000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>659000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>635100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>627000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>609000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>628000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>616200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3503000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3507000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3553000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3497300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3524000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3487300</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>311000</v>
+        <v>307000</v>
       </c>
       <c r="E49" s="3">
         <v>311000</v>
       </c>
       <c r="F49" s="3">
+        <v>311000</v>
+      </c>
+      <c r="G49" s="3">
         <v>321300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>285000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>288000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>245000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>220800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>222000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>219000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>223000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>225000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>208000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>214000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>217000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1500</v>
-      </c>
-      <c r="S49" s="3">
-        <v>1000</v>
       </c>
       <c r="T49" s="3">
         <v>1000</v>
@@ -4591,10 +4702,10 @@
         <v>1000</v>
       </c>
       <c r="V49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W49" s="3">
         <v>1200</v>
-      </c>
-      <c r="W49" s="3">
-        <v>1000</v>
       </c>
       <c r="X49" s="3">
         <v>1000</v>
@@ -4603,10 +4714,10 @@
         <v>1000</v>
       </c>
       <c r="Z49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA49" s="3">
         <v>1300</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>2000</v>
       </c>
       <c r="AB49" s="3">
         <v>2000</v>
@@ -4615,28 +4726,31 @@
         <v>2000</v>
       </c>
       <c r="AD49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AE49" s="3">
         <v>1600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>362000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>364000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>366000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>376800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>359000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>356200</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4960,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E52" s="3">
         <v>80000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>88000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>38500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>145000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>114000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>86000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>39800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>96000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>126000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>138000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>109000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>124000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>137000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>114000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>124100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>590000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>573000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>454000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>373100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>202000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>198000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>194000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>189800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>187000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>182000</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>175000</v>
       </c>
       <c r="AD52" s="3">
         <v>175000</v>
       </c>
       <c r="AE52" s="3">
+        <v>175000</v>
+      </c>
+      <c r="AF52" s="3">
         <v>153000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>161000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>212000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>201900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>129000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>176700</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5174,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4111000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3994000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4053000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4108400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3916000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4091000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4173000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3772100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4561000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4666000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4520000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4039000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3867000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3248000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3160000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2482300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2033000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1913000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1550000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1508400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1651000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1530000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1489000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1455100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1661000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1769000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1824000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2525900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5359000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5211000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5185000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5137800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5263000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5054900</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,216 +5361,223 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>129000</v>
+      </c>
+      <c r="E57" s="3">
         <v>198000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>179000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>70700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>231000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>222000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>206000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>95000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>122000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>108000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>126000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>342500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>138000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>136000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>154000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>128200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>68000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>54000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>34000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>36000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>62000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>61000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>58000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>47700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>65000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>49000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>42000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>58900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>260000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>226000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>289000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>285600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>336000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>283300</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E58" s="3">
         <v>108000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>114000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>174600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>130000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>106000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>99000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>56700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>54000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>51000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>41000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>38000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>429000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>50000</v>
       </c>
       <c r="Q58" s="3">
         <v>50000</v>
       </c>
       <c r="R58" s="3">
+        <v>50000</v>
+      </c>
+      <c r="S58" s="3">
         <v>46500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>48000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>47000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>105000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>45600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>40000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>36000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>28000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>23200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>23000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>79000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>86000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>448000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>225000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>322000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>501000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>482800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>364000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5448,415 +5585,427 @@
         <v>2000</v>
       </c>
       <c r="E59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F59" s="3">
         <v>203000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10100</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1000</v>
       </c>
       <c r="H59" s="3">
         <v>1000</v>
       </c>
       <c r="I59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J59" s="3">
         <v>152000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>23000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>574000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>26000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>426600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>45000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>34000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>28000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>53200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>33000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>27000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>25000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>23400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>36000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>16000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>28000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>19000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>17000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>106000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>125000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>299500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>179000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>213000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>251000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>276300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>343000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>332100</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>241000</v>
+      </c>
+      <c r="E60" s="3">
         <v>308000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>496000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>358800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>362000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>329000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>457000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>193000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>199000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>733000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>193000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>447000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>612000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>220000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>232000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>227900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>149000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>128000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>164000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>105000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>138000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>113000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>114000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>89900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>105000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>234000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>253000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>806300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>664000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>761000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1041000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1044800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1043000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>955200</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1421000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1412000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1436000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1416900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1309000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1325000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1223000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1144000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1101000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1117000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1192000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1172000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1094000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1042000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1001000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>871800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>714000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>688000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>555000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>576700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>586000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>582000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>575000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>563200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>585000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>564000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>584000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>588500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3344000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3170000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2892000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2829600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2941000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2820000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E62" s="3">
         <v>168000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>126000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>125900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>41000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>39000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>43000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>41400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>151000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>177000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>174000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>168000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>151000</v>
-      </c>
-      <c r="P62" s="3">
-        <v>156000</v>
       </c>
       <c r="Q62" s="3">
         <v>156000</v>
       </c>
       <c r="R62" s="3">
+        <v>156000</v>
+      </c>
+      <c r="S62" s="3">
         <v>106600</v>
-      </c>
-      <c r="S62" s="3">
-        <v>124000</v>
       </c>
       <c r="T62" s="3">
         <v>124000</v>
       </c>
       <c r="U62" s="3">
+        <v>124000</v>
+      </c>
+      <c r="V62" s="3">
         <v>121000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>114900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>109000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>102000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>99000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>86200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>88000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>84000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>85000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>79600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>360000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>375000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>363000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>369200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>345000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>336300</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6322,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1978000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2018000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2190000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2038200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1849000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1822000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1853000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1476100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2128000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2534000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2084000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2245000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2286000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1858000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1846000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1415500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1073000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1022000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>921000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>885000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>936000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>879000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>855000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>806100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>848000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>949000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>997000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1542700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4622000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4522000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4514000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4456600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4545000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4321100</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6896,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1051000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1007000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>895000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1087000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1083000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1303000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1349000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1504600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2384000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2079000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1814000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1166000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>960000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>770000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>699000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>448500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>360000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>293000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>11000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>92000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>42000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>33000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>45800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>207000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>229000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>258000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-282500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-531000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-575000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-584000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-564500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-533000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-513100</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7324,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1164000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1117000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1006000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1203300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1200000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1420000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1470000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1598500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2433000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2132000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2436000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1794000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1581000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1390000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1314000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1066800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>960000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>891000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>629000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>623400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>715000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>651000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>634000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>649000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>813000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>820000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>827000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>983100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>737000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>689000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>671000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>681200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>718000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>733800</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E81" s="3">
         <v>112000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-205000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-30000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-842300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>251000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>265000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>639000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>392300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>538000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>172000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>180000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>145100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>67000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>279000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>15000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-23400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>28000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-61800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-29000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>545000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>236600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-23000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>9000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-411900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-48000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7798,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E83" s="3">
         <v>23000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7300</v>
-      </c>
-      <c r="G83" s="3">
-        <v>15000</v>
       </c>
       <c r="H83" s="3">
         <v>15000</v>
       </c>
       <c r="I83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="J83" s="3">
         <v>14000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3400</v>
-      </c>
-      <c r="K83" s="3">
-        <v>15000</v>
       </c>
       <c r="L83" s="3">
         <v>15000</v>
       </c>
       <c r="M83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="N83" s="3">
         <v>14000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>43000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>16000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>11200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>9000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>7000</v>
       </c>
       <c r="U83" s="3">
         <v>7000</v>
       </c>
       <c r="V83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="W83" s="3">
         <v>9100</v>
-      </c>
-      <c r="W83" s="3">
-        <v>8000</v>
       </c>
       <c r="X83" s="3">
         <v>8000</v>
       </c>
       <c r="Y83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Z83" s="3">
         <v>7000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>7400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>8000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>7000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>178500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>43000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>44000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>48000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>172400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>48200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>41900</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8438,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>126000</v>
+      </c>
+      <c r="E89" s="3">
         <v>17000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>70000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>76000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>163000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>26000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>48400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>163000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>542000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>18000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>107500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>133000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>28000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>22000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>35000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>33000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>15000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>35000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>47000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>163400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>10000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>13000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-134000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>391900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>40000</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>101000</v>
       </c>
       <c r="AG89" s="3">
         <v>101000</v>
       </c>
       <c r="AH89" s="3">
+        <v>101000</v>
+      </c>
+      <c r="AI89" s="3">
         <v>162300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>65600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>52300</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8586,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-188000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-68000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-69000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-133100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-60000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-86000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-53000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-65300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-60000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-78000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-87000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-80700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-61000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-46000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-45000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-24500</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-11000</v>
       </c>
       <c r="T91" s="3">
         <v>-11000</v>
       </c>
       <c r="U91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="V91" s="3">
         <v>-28000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-36300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-227600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-40000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-290600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-103300</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8905,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-142000</v>
+      </c>
+      <c r="E94" s="3">
         <v>72000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-35000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-118200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-42000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-241000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-31000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-70400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-80000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-430000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>377000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-61500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-144000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-52000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-98000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-327600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-16000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>211000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-89000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>50000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>3000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-46000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-197400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-115000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>217000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>584500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>3000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-62000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-114000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-399600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-36300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-167400</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,59 +9053,60 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>201000</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>400</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>150000</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>-552000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-189000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-100000</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-114100</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -8924,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9479,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-178000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-56000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>166600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>16000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-78000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>220000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-369000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>21000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-150000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-304400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>451000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-129000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>254000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>162800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>13000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>44000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>36000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-109600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>31000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>13000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-108600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-50000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1049000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>97100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>90000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>3000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>174600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>119200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4000</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="F101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-10000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-6000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>9700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-10000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-6000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>9700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>8000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-9000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>9600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>3000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>17300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>11000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>5400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-91000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-20000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>63700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>43000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-160000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>215000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-287000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>123000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>239000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-248600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>437000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-145000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>169000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-146000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>34000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>286000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-35000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-63000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>72000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-23000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>30000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-144300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-154000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-962000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1090800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>132000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>38000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-57300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>149900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-87500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>KEN</t>
   </si>
@@ -656,480 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>159300</v>
+      </c>
+      <c r="E8" s="3">
         <v>237000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>181000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>174000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>150800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>229000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>165000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>147000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>145000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>163000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>121000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>146000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>134800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>353000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>105000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>115000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>104500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>117000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>76000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>89000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>89500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>102000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>85000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>97000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>85000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>94000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>84000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>101000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>365700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>97000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>84000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>93000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>324300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>502000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>459300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>118900</v>
+      </c>
+      <c r="E9" s="3">
         <v>157000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>129000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>117000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>112300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>151000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>129000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>103000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>104300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>130000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>113000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>110000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>110400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>279000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>93000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>92000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>90200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>93000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>66000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>65000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>69200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>77000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>72000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>68000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>78300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>69000</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>71000</v>
       </c>
       <c r="AD9" s="3">
         <v>71000</v>
       </c>
       <c r="AE9" s="3">
+        <v>71000</v>
+      </c>
+      <c r="AF9" s="3">
         <v>297200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>76000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>75000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>72000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>278400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>399000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>381600</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E10" s="3">
         <v>80000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>52000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>57000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>38500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>78000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>36000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>44000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>40700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>33000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>36000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>24400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>74000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>23000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>14300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>24000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>10000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>24000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>20300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>25000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>13000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>29000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>25000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>13000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>30000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>68500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>21000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>9000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>21000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>45900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>103000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>77700</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1274,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,25 +1397,28 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>64300</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-111000</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>100</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>-800</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1407,14 +1426,14 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>930400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1431,95 +1450,98 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>-43500</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>-6000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>400</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>-63000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-28800</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>20000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>72300</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>72300</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E15" s="3">
         <v>24000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>22000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20000</v>
       </c>
-      <c r="G15" s="3">
-        <v>25200</v>
-      </c>
       <c r="H15" s="3">
+        <v>21000</v>
+      </c>
+      <c r="I15" s="3">
         <v>25000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>17000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>21100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1595,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>156800</v>
+      </c>
+      <c r="E17" s="3">
         <v>200000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>172000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>168000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>142200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>197000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>171000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>140000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>156100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>149000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>136000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>132000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>121200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>332000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>120000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>102000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>69000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>102000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>76000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>67000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>74400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>73000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>79000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>78000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>93300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>75000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>76000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>15000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>323400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>87000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>90000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>79000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>395200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>432000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>491100</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E18" s="3">
         <v>37000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>32000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>21000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-15000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>35500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>15000</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
       <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
         <v>22000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>15100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>29000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>6000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>19000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>19000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>8000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>86000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>42300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>10000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>14000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-70900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>70000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-31800</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,252 +1916,259 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-545100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-57000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-20000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-5300</v>
-      </c>
       <c r="H20" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="I20" s="3">
         <v>201000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>27000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-12000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-144700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>273000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>274000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>659000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>383100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>462000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>160000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>163000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>95900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>50000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>278000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-30700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-52800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-36000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>472000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-177900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-42000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-356000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-94000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-239100</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>567200</v>
+      </c>
+      <c r="E21" s="3">
         <v>118000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>35000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>46000</v>
       </c>
-      <c r="G21" s="3">
-        <v>39100</v>
-      </c>
       <c r="H21" s="3">
+        <v>34000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-144000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>33000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>154600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>302000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>274000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>687000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>411300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>526000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>161000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>189000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>142600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>74000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>285000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>32000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-6400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>24000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-53600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-21000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>566000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>42800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>27000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>18000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>20000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-254500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>24200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-228900</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E22" s="3">
         <v>52000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>31000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>21000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>-2700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>23000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8500</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -2205,222 +2244,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>489600</v>
+      </c>
+      <c r="E23" s="3">
         <v>60000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>107000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>17000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-181000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-40000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>18000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-831400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>287000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>259000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>673000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>396600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>483000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>145000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>176000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>131400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>65000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>278000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>25000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-15500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>16000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-61000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>558000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-135600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-26000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-28000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-426900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-24000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-270900</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E24" s="3">
         <v>6000</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>13000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>16000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>16000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>22300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-9000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-3300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3000</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>5000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>72800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4000</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
       <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>4000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>19000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>463100</v>
+      </c>
+      <c r="E26" s="3">
         <v>54000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>107000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-190000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-37000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-835300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>271000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>257000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>657000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>374300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>501000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>154000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>178000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>134700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>62000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>278000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>20000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-18200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>9000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-61500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-29000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>552000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-208400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-20000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-26000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-32000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-429200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-43000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-280000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>434700</v>
+      </c>
+      <c r="E27" s="3">
         <v>43000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>112000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-205000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-30000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-842300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>251000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>265000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>639000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>392300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>538000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>172000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>180000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>144600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>59000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>279000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>15000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-22000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-60200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-29000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>545000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-240000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-20000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-38000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-42000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-447100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-48000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2879,83 +2939,86 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3">
         <v>500</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>8000</v>
       </c>
-      <c r="U29" s="3" t="s">
+      <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-1300</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>26000</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>-1000</v>
       </c>
       <c r="Z29" s="3">
         <v>-1000</v>
       </c>
       <c r="AA29" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>476600</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>47000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>22000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>35200</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,222 +3234,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>545100</v>
+      </c>
+      <c r="E32" s="3">
         <v>57000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>20000</v>
       </c>
-      <c r="G32" s="3">
-        <v>5300</v>
-      </c>
       <c r="H32" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-201000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-27000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>12000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>144700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-273000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-274000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-659000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-383100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-462000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-160000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-163000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-95900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-50000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-278000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>30700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>13000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>11000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>20000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>52800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>26000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>36000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-472000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>177900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>26000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>20000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>42000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>356000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>94000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>239100</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>434700</v>
+      </c>
+      <c r="E33" s="3">
         <v>43000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>112000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-205000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-30000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-842300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>251000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>265000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>639000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>392300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>538000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>172000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>180000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>145100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>67000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>279000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>15000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-23400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>28000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-61800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-29000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>545000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>236600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-23000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>9000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-411900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-48000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>434700</v>
+      </c>
+      <c r="E35" s="3">
         <v>43000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>112000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-205000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-30000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-842300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>251000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>265000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>639000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>392300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>538000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>172000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>180000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>145100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>67000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>279000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>15000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-23400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>28000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-61800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-29000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>545000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>236600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-23000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>9000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-411900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-48000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,329 +3871,339 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1015900</v>
+      </c>
+      <c r="E41" s="3">
         <v>615000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>586000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>677000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>696800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>633000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>590000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>750000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>535200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>550000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>837000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>714000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>475000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>723000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>310000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>455000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>286200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>432000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>398000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>111000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>147200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>210000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>138000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>161000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>131100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>275000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>429000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>455000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1417400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>498000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>366000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>328000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>326600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>451000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>301100</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>142600</v>
+      </c>
+      <c r="E42" s="3">
         <v>158000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>165000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>193000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>215800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>252000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>279000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>315000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>380400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>368000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>11000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>39000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>15000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>22000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>564200</v>
-      </c>
-      <c r="T42" s="3">
-        <v>16000</v>
       </c>
       <c r="U42" s="3">
         <v>16000</v>
       </c>
       <c r="V42" s="3">
+        <v>16000</v>
+      </c>
+      <c r="W42" s="3">
         <v>22000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>33600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>72000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>78000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>51000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>49900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>28000</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
-      </c>
       <c r="AD42" s="3">
         <v>0</v>
       </c>
       <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3">
         <v>7100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>50000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>54000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>110000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>89500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>85000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>85300</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>90900</v>
+      </c>
+      <c r="E43" s="3">
         <v>97000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>96000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>67000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>150800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>80000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>75000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>53000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>78600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>52000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>48000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>530000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>63000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>55000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>99000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>44000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>47900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>33000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>31000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>29000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>39300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>34000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>32000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>33000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>35500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>43000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>31000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>35000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>44400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>383000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>280000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>289000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>296000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>271000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>266300</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4136,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4197,506 +4292,521 @@
         <v>0</v>
       </c>
       <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
         <v>83000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>82000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>89000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>91700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>87000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E45" s="3">
         <v>41000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>101000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>106000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>19200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>45000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>54000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>209000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>47200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>64000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>403000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>43000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>44000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>48000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>220000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>29000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>21400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>20000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>19000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>131000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>109500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>147000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>116000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>100000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>111100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>21000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>18000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>20000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>35800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>40000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>102000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>53000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>49800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>62000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1262700</v>
+      </c>
+      <c r="E46" s="3">
         <v>911000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>948000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1043000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1096000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1010000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>998000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1327000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1061700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1034000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1299000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1291000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>582000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>865000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>644000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>550000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>919800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>501000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>464000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>293000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>329500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>463000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>364000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>345000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>327700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>367000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>478000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>510000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1504600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1054000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>884000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>869000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>853600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>956000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>809900</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1458600</v>
+      </c>
+      <c r="E47" s="3">
         <v>693000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>708000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>700000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>703200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>696000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>901000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>929000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1079400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1966000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1807000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1611000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1899000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1571000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1209000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1261000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>532400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>137000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>91000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>118000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>119700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>304000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>297000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>290000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>301200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>478000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>498000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>509000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>228400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>287000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>295000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>185000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>208200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>295000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>224800</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1331700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2108000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1937000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1902000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1889300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1771000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1784000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1581000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1349200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1243000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1215000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1257000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1224000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1099000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1044000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1018000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>904600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>804000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>784000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>684000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>684800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>681000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>670000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>659000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>635100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>627000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>609000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>628000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>616200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3503000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3507000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3553000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3497300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3524000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3487300</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E49" s="3">
         <v>307000</v>
-      </c>
-      <c r="E49" s="3">
-        <v>311000</v>
       </c>
       <c r="F49" s="3">
         <v>311000</v>
       </c>
       <c r="G49" s="3">
+        <v>311000</v>
+      </c>
+      <c r="H49" s="3">
         <v>321300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>285000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>288000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>245000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>220800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>222000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>219000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>223000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>225000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>208000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>214000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>217000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1500</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1000</v>
       </c>
       <c r="U49" s="3">
         <v>1000</v>
@@ -4705,10 +4815,10 @@
         <v>1000</v>
       </c>
       <c r="W49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X49" s="3">
         <v>1200</v>
-      </c>
-      <c r="X49" s="3">
-        <v>1000</v>
       </c>
       <c r="Y49" s="3">
         <v>1000</v>
@@ -4717,10 +4827,10 @@
         <v>1000</v>
       </c>
       <c r="AA49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB49" s="3">
         <v>1300</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>2000</v>
       </c>
       <c r="AC49" s="3">
         <v>2000</v>
@@ -4729,28 +4839,31 @@
         <v>2000</v>
       </c>
       <c r="AE49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AF49" s="3">
         <v>1600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>362000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>364000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>366000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>376800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>359000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>356200</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E52" s="3">
         <v>83000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>80000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>88000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>38500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>145000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>114000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>86000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>39800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>96000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>126000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>138000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>109000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>124000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>137000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>114000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>124100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>590000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>573000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>454000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>373100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>202000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>198000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>194000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>189800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>187000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>182000</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>175000</v>
       </c>
       <c r="AE52" s="3">
         <v>175000</v>
       </c>
       <c r="AF52" s="3">
+        <v>175000</v>
+      </c>
+      <c r="AG52" s="3">
         <v>153000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>161000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>212000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>201900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>129000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>176700</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4213200</v>
+      </c>
+      <c r="E54" s="3">
         <v>4111000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3994000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4053000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4108400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3916000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4091000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4173000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3772100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4561000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4666000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4520000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4039000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3867000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3248000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3160000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2482300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2033000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1913000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1550000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1508400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1651000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1530000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1489000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1455100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1661000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1769000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1824000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2525900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5359000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5211000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5185000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5137800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5263000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5054900</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,650 +5491,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>58300</v>
+      </c>
+      <c r="E57" s="3">
         <v>129000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>198000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>179000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>70700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>231000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>222000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>206000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>95000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>122000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>108000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>126000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>342500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>138000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>136000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>154000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>128200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>68000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>54000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>34000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>36000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>62000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>61000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>58000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>47700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>65000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>49000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>42000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>58900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>260000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>226000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>289000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>285600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>336000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>283300</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>88500</v>
+      </c>
+      <c r="E58" s="3">
         <v>110000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>108000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>114000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>174600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>130000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>106000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>99000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>56700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>54000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>51000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>41000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>38000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>429000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>50000</v>
       </c>
       <c r="R58" s="3">
         <v>50000</v>
       </c>
       <c r="S58" s="3">
+        <v>50000</v>
+      </c>
+      <c r="T58" s="3">
         <v>46500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>48000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>47000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>105000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>45600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>40000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>36000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>28000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>23200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>23000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>79000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>86000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>448000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>225000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>322000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>501000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>482800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>364000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="E59" s="3">
         <v>2000</v>
       </c>
       <c r="F59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G59" s="3">
         <v>203000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1000</v>
       </c>
       <c r="I59" s="3">
         <v>1000</v>
       </c>
       <c r="J59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K59" s="3">
         <v>152000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>23000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>574000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>26000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>426600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>45000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>34000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>28000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>53200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>33000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>27000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>25000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>23400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>36000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>16000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>28000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>19000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>17000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>106000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>125000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>299500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>179000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>213000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>251000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>276300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>343000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>332100</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>182800</v>
+      </c>
+      <c r="E60" s="3">
         <v>241000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>308000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>496000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>358800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>362000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>329000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>457000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>193000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>199000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>733000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>193000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>447000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>612000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>220000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>232000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>227900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>149000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>128000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>164000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>105000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>138000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>113000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>114000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>89900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>105000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>234000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>253000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>806300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>664000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>761000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1041000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1044800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1043000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>955200</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1191600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1421000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1412000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1436000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1416900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1309000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1325000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1223000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1144000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1101000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1117000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1192000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1172000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1094000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1042000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1001000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>871800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>714000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>688000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>555000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>576700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>586000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>582000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>575000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>563200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>585000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>564000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>584000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>588500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3344000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3170000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2892000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2829600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2941000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2820000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E62" s="3">
         <v>178000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>168000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>126000</v>
       </c>
-      <c r="G62" s="3">
-        <v>125900</v>
-      </c>
       <c r="H62" s="3">
+        <v>46900</v>
+      </c>
+      <c r="I62" s="3">
         <v>41000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>39000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>43000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>41400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>151000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>177000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>174000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>168000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>151000</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>156000</v>
       </c>
       <c r="R62" s="3">
         <v>156000</v>
       </c>
       <c r="S62" s="3">
+        <v>156000</v>
+      </c>
+      <c r="T62" s="3">
         <v>106600</v>
-      </c>
-      <c r="T62" s="3">
-        <v>124000</v>
       </c>
       <c r="U62" s="3">
         <v>124000</v>
       </c>
       <c r="V62" s="3">
+        <v>124000</v>
+      </c>
+      <c r="W62" s="3">
         <v>121000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>114900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>109000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>102000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>99000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>86200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>88000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>84000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>85000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>79600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>360000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>375000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>363000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>369200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>345000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>336300</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1553700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1978000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2018000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2190000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2038200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1849000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1822000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1853000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1476100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2128000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2534000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2084000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2245000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2286000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1858000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1846000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1415500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1073000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1022000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>921000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>885000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>936000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>879000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>855000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>806100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>848000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>949000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>997000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1542700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4622000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4522000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4514000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4456600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4545000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4321100</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1491200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1051000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1007000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>895000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1087000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1083000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1303000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1349000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1504600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2384000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2079000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1814000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1166000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>960000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>770000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>699000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>448500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>360000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>293000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>11000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>92000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>42000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>33000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>45800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>207000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>229000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>258000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-282500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-531000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-575000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-584000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-564500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-533000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-513100</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1607900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1164000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1117000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1006000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1203300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1200000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1420000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1470000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1598500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2433000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2132000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2436000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1794000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1581000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1390000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1314000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1066800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>960000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>891000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>629000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>623400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>715000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>651000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>634000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>649000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>813000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>820000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>827000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>983100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>737000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>689000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>671000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>681200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>718000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>733800</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>434700</v>
+      </c>
+      <c r="E81" s="3">
         <v>43000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>112000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-205000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-30000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-842300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>251000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>265000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>639000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>392300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>538000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>172000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>180000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>145100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>67000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>279000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>15000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-23400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>28000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-61800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-29000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>545000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>236600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-23000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>9000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-411900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-48000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E83" s="3">
         <v>28000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>23000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7300</v>
-      </c>
-      <c r="H83" s="3">
-        <v>15000</v>
       </c>
       <c r="I83" s="3">
         <v>15000</v>
       </c>
       <c r="J83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="K83" s="3">
         <v>14000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3400</v>
-      </c>
-      <c r="L83" s="3">
-        <v>15000</v>
       </c>
       <c r="M83" s="3">
         <v>15000</v>
       </c>
       <c r="N83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="O83" s="3">
         <v>14000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>14600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>43000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>16000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>11200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>9000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>7000</v>
       </c>
       <c r="V83" s="3">
         <v>7000</v>
       </c>
       <c r="W83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="X83" s="3">
         <v>9100</v>
-      </c>
-      <c r="X83" s="3">
-        <v>8000</v>
       </c>
       <c r="Y83" s="3">
         <v>8000</v>
       </c>
       <c r="Z83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="AA83" s="3">
         <v>7000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>7400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>8000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>7000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>8000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>178500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>43000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>44000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>48000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>172400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>48200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>41900</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E89" s="3">
         <v>126000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>70000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>76000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>163000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>26000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>48400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>163000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>542000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>18000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>107500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>133000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>28000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>22000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>35000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>33000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>15000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>35000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>47000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>163400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>10000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>13000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-134000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>391900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>40000</v>
-      </c>
-      <c r="AG89" s="3">
-        <v>101000</v>
       </c>
       <c r="AH89" s="3">
         <v>101000</v>
       </c>
       <c r="AI89" s="3">
+        <v>101000</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>162300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>65600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>52300</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-188000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-68000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-69000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-133100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-60000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-86000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-53000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-65300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-60000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-78000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-87000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-80700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-61000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-46000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-45000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-24500</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-11000</v>
       </c>
       <c r="U91" s="3">
         <v>-11000</v>
       </c>
       <c r="V91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="W91" s="3">
         <v>-28000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-36300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-227600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-40000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-290600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-103300</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>240900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-142000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>72000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-35000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-118200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-42000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-241000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-31000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-70400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-80000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-430000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>377000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-61500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-144000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-52000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-98000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-327600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-16000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>211000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-89000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>50000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>3000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-46000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-197400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-115000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>217000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>584500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>3000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-62000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-114000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-399600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-36300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-167400</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,62 +9286,63 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>201000</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>400</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>150000</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
         <v>-552000</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-189000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-100000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-114100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -9161,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>105900</v>
+      </c>
+      <c r="E100" s="3">
         <v>44000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-178000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-56000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>166600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>16000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-78000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>220000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-369000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>21000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-150000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-304400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>451000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-129000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>254000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>162800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>13000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>44000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>36000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-109600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>31000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>13000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-108600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-50000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1049000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>97100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>90000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>3000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>174600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>119200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4000</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="G101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-10000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>9700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-10000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-6000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>9700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>8000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-9000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>9600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>3000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>3000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>4000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>17300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>3000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>11000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>401000</v>
+      </c>
+      <c r="E102" s="3">
         <v>29000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-91000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-20000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>63700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>43000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-160000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>215000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-14400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-287000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>123000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>239000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-248600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>437000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-145000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>169000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-146000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>34000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>286000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-35000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-63000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>72000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-23000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>30000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-144300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-154000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-26000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-962000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1090800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>132000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>38000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-57300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>149900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-87500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
   <si>
     <t>KEN</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
         <v>159300</v>
       </c>
-      <c r="E8" s="3">
-        <v>237000</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3">
         <v>181000</v>
       </c>
-      <c r="G8" s="3">
-        <v>174000</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3">
         <v>150800</v>
       </c>
-      <c r="I8" s="3">
-        <v>229000</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>165000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>147000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>145000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>163000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>121000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>146000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>134800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>353000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>105000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>115000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>104500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>117000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>76000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>89000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>89500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>102000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>85000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>97000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>85000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>94000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>84000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>101000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>365700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>97000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>84000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>93000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>324300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>502000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>459300</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
         <v>118900</v>
       </c>
-      <c r="E9" s="3">
-        <v>157000</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3">
         <v>129000</v>
       </c>
-      <c r="G9" s="3">
-        <v>117000</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3">
         <v>112300</v>
       </c>
-      <c r="I9" s="3">
-        <v>151000</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>129000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>103000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>104300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>130000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>113000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>110000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>110400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>279000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>93000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>92000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>90200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>93000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>66000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>65000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>69200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>77000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>72000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>68000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>78300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>69000</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>71000</v>
       </c>
       <c r="AE9" s="3">
         <v>71000</v>
       </c>
       <c r="AF9" s="3">
+        <v>71000</v>
+      </c>
+      <c r="AG9" s="3">
         <v>297200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>76000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>75000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>72000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>278400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>399000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>381600</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
         <v>40400</v>
       </c>
-      <c r="E10" s="3">
-        <v>80000</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3">
         <v>52000</v>
       </c>
-      <c r="G10" s="3">
-        <v>57000</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3">
         <v>38500</v>
       </c>
-      <c r="I10" s="3">
-        <v>78000</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>36000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>44000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>40700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>33000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>36000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>24400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>74000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>12000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>23000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>14300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>24000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>24000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>20300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>25000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>13000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>29000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>6700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>25000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>13000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>30000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>68500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>21000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>9000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>45900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>103000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>77700</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,43 +1417,46 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>64300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>-111000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>-800</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>930400</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1453,98 +1473,101 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>-43500</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>-6000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>400</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-63000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-28800</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>72300</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>72300</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>19600</v>
       </c>
-      <c r="E15" s="3">
-        <v>24000</v>
-      </c>
       <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
         <v>22000</v>
       </c>
-      <c r="G15" s="3">
-        <v>20000</v>
-      </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>21000</v>
       </c>
-      <c r="I15" s="3">
-        <v>25000</v>
-      </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>17000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>14000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>21100</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3">
         <v>156800</v>
       </c>
-      <c r="E17" s="3">
-        <v>200000</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3">
         <v>172000</v>
       </c>
-      <c r="G17" s="3">
-        <v>168000</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3">
         <v>142200</v>
       </c>
-      <c r="I17" s="3">
-        <v>197000</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>171000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>140000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>156100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>149000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>136000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>132000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>121200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>332000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>120000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>102000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>69000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>102000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>76000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>67000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>74400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>73000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>79000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>78000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>93300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>75000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>76000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>15000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>323400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>87000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>90000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>79000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>395200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>432000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>491100</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3">
         <v>2500</v>
       </c>
-      <c r="E18" s="3">
-        <v>37000</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3">
         <v>9000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3">
+        <v>8600</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>7000</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="N18" s="3">
+        <v>14000</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="P18" s="3">
+        <v>14000</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>13600</v>
+      </c>
+      <c r="R18" s="3">
+        <v>21000</v>
+      </c>
+      <c r="S18" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="T18" s="3">
+        <v>13000</v>
+      </c>
+      <c r="U18" s="3">
+        <v>35500</v>
+      </c>
+      <c r="V18" s="3">
+        <v>15000</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
+        <v>22000</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>15100</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>29000</v>
+      </c>
+      <c r="AA18" s="3">
         <v>6000</v>
       </c>
-      <c r="H18" s="3">
-        <v>8600</v>
-      </c>
-      <c r="I18" s="3">
-        <v>32000</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="AB18" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>8000</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>86000</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>42300</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AI18" s="3">
         <v>-6000</v>
       </c>
-      <c r="K18" s="3">
-        <v>7000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-11200</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="AJ18" s="3">
         <v>14000</v>
       </c>
-      <c r="N18" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="O18" s="3">
-        <v>14000</v>
-      </c>
-      <c r="P18" s="3">
-        <v>13600</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>21000</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="S18" s="3">
-        <v>13000</v>
-      </c>
-      <c r="T18" s="3">
-        <v>35500</v>
-      </c>
-      <c r="U18" s="3">
-        <v>15000</v>
-      </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
-      <c r="W18" s="3">
-        <v>22000</v>
-      </c>
-      <c r="X18" s="3">
-        <v>15100</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>29000</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>6000</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>19000</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>19000</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>8000</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>86000</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>42300</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>10000</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="AI18" s="3">
-        <v>14000</v>
-      </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-70900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>70000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-31800</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,261 +1950,268 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
         <v>-545100</v>
       </c>
-      <c r="E20" s="3">
-        <v>-57000</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3">
         <v>-4000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
+        <v>27000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-144700</v>
+      </c>
+      <c r="N20" s="3">
+        <v>273000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>274000</v>
+      </c>
+      <c r="P20" s="3">
+        <v>659000</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>383100</v>
+      </c>
+      <c r="R20" s="3">
+        <v>462000</v>
+      </c>
+      <c r="S20" s="3">
+        <v>160000</v>
+      </c>
+      <c r="T20" s="3">
+        <v>163000</v>
+      </c>
+      <c r="U20" s="3">
+        <v>95900</v>
+      </c>
+      <c r="V20" s="3">
+        <v>50000</v>
+      </c>
+      <c r="W20" s="3">
+        <v>278000</v>
+      </c>
+      <c r="X20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-20000</v>
       </c>
-      <c r="H20" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>201000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>27000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-144700</v>
-      </c>
-      <c r="M20" s="3">
-        <v>273000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>274000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>659000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>383100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>462000</v>
-      </c>
-      <c r="R20" s="3">
-        <v>160000</v>
-      </c>
-      <c r="S20" s="3">
-        <v>163000</v>
-      </c>
-      <c r="T20" s="3">
-        <v>95900</v>
-      </c>
-      <c r="U20" s="3">
-        <v>50000</v>
-      </c>
-      <c r="V20" s="3">
-        <v>278000</v>
-      </c>
-      <c r="W20" s="3">
-        <v>3000</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-30700</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
+        <v>-52800</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>472000</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>-177900</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB20" s="3">
-        <v>-52800</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-26000</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-36000</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>472000</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>-177900</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-26000</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>-20000</v>
-      </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-42000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-356000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-94000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-239100</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>567200</v>
       </c>
-      <c r="E21" s="3">
-        <v>118000</v>
-      </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>35000</v>
       </c>
-      <c r="G21" s="3">
-        <v>46000</v>
-      </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>34000</v>
       </c>
-      <c r="I21" s="3">
-        <v>-144000</v>
-      </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>-16000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>33000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>154600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>302000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>274000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>687000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>411300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>526000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>161000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>189000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>142600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>74000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>285000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>32000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>24000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-53600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-21000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>566000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>42800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>27000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>18000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-254500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>24200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-228900</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3">
         <v>-18300</v>
       </c>
-      <c r="E22" s="3">
-        <v>52000</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3">
         <v>31000</v>
       </c>
-      <c r="G22" s="3">
-        <v>21000</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3">
         <v>-2700</v>
       </c>
-      <c r="I22" s="3">
-        <v>23000</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>18000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8500</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -2247,228 +2287,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3">
         <v>489600</v>
       </c>
-      <c r="E23" s="3">
-        <v>60000</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3">
         <v>107000</v>
       </c>
-      <c r="G23" s="3">
-        <v>17000</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3">
         <v>18300</v>
       </c>
-      <c r="I23" s="3">
-        <v>-181000</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>-40000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>18000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-831400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>287000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>259000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>673000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>396600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>483000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>145000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>176000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>131400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>65000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>278000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>25000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-15500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>16000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-61000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-28000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>558000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-135600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-26000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-28000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-426900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-24000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-270900</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3">
         <v>26600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="L24" s="3">
+        <v>13000</v>
+      </c>
+      <c r="M24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>16000</v>
+      </c>
+      <c r="O24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P24" s="3">
+        <v>16000</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>22300</v>
+      </c>
+      <c r="R24" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="S24" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="T24" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="U24" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="V24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF24" s="3">
         <v>6000</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="3">
-        <v>7000</v>
-      </c>
-      <c r="H24" s="3">
-        <v>6200</v>
-      </c>
-      <c r="I24" s="3">
-        <v>9000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="K24" s="3">
-        <v>13000</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="AG24" s="3">
+        <v>72800</v>
+      </c>
+      <c r="AH24" s="3">
         <v>4000</v>
       </c>
-      <c r="M24" s="3">
-        <v>16000</v>
-      </c>
-      <c r="N24" s="3">
-        <v>2000</v>
-      </c>
-      <c r="O24" s="3">
-        <v>16000</v>
-      </c>
-      <c r="P24" s="3">
-        <v>22300</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>-18000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="S24" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="U24" s="3">
-        <v>3000</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3">
-        <v>5000</v>
-      </c>
-      <c r="X24" s="3">
-        <v>2700</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>7000</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>500</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>4000</v>
       </c>
-      <c r="AD24" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>6000</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>72800</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>4000</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="3">
-        <v>4000</v>
-      </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>2300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>19000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
         <v>463100</v>
       </c>
-      <c r="E26" s="3">
-        <v>54000</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3">
         <v>107000</v>
       </c>
-      <c r="G26" s="3">
-        <v>10000</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3">
         <v>12100</v>
       </c>
-      <c r="I26" s="3">
-        <v>-190000</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>-37000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-835300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>271000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>257000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>657000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>374300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>501000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>154000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>178000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>134700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>62000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>278000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>20000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-18200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>9000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-61500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-29000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>552000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-208400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-26000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-32000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-429200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-43000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-280000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
         <v>434700</v>
       </c>
-      <c r="E27" s="3">
-        <v>43000</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3">
         <v>112000</v>
       </c>
-      <c r="G27" s="3">
-        <v>8000</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3">
         <v>7000</v>
       </c>
-      <c r="I27" s="3">
-        <v>-205000</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>-30000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-842300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>251000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>265000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>639000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>392300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>538000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>172000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>180000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>144600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>59000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>279000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>15000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-60200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-29000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>545000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-240000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-38000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-42000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-447100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-48000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2942,83 +3003,86 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="3">
         <v>500</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>8000</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>26000</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA29" s="3">
         <v>-1000</v>
       </c>
       <c r="AB29" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>476600</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>47000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>22000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>35200</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
         <v>545100</v>
       </c>
-      <c r="E32" s="3">
-        <v>57000</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3">
         <v>4000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
+        <v>4500</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>12000</v>
+      </c>
+      <c r="M32" s="3">
+        <v>144700</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-273000</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-274000</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-659000</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-383100</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-462000</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-160000</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-163000</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-95900</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-50000</v>
+      </c>
+      <c r="W32" s="3">
+        <v>-278000</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>30700</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>13000</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AB32" s="3">
         <v>20000</v>
       </c>
-      <c r="H32" s="3">
-        <v>4500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-201000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-27000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>12000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>144700</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-273000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-274000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-659000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-383100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-462000</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-160000</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-163000</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-95900</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-50000</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-278000</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="X32" s="3">
-        <v>30700</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>13000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>11000</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
+        <v>52800</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>26000</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>36000</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>-472000</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>177900</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>26000</v>
+      </c>
+      <c r="AI32" s="3">
         <v>20000</v>
       </c>
-      <c r="AB32" s="3">
-        <v>52800</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>26000</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>36000</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-472000</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>177900</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>26000</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>20000</v>
-      </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>42000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>356000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>94000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>239100</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
         <v>434700</v>
       </c>
-      <c r="E33" s="3">
-        <v>43000</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3">
         <v>112000</v>
       </c>
-      <c r="G33" s="3">
-        <v>8000</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3">
         <v>7000</v>
       </c>
-      <c r="I33" s="3">
-        <v>-205000</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>-30000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-842300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>251000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>265000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>639000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>392300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>538000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>172000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>180000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>145100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>67000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>279000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>15000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-23400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>28000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-61800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-29000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>545000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>236600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-23000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>9000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-411900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-48000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
         <v>434700</v>
       </c>
-      <c r="E35" s="3">
-        <v>43000</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3">
         <v>112000</v>
       </c>
-      <c r="G35" s="3">
-        <v>8000</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3">
         <v>7000</v>
       </c>
-      <c r="I35" s="3">
-        <v>-205000</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>-30000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-842300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>251000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>265000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>639000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>392300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>538000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>172000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>180000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>145100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>67000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>279000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>15000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-23400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>28000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-61800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-29000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>545000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>236600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-23000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>9000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-411900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-48000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,338 +3958,348 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3">
         <v>1015900</v>
       </c>
-      <c r="E41" s="3">
-        <v>615000</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="3">
         <v>586000</v>
       </c>
-      <c r="G41" s="3">
-        <v>677000</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3">
         <v>696800</v>
       </c>
-      <c r="I41" s="3">
-        <v>633000</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K41" s="3">
         <v>590000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>750000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>535200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>550000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>837000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>714000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>475000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>723000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>310000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>455000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>286200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>432000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>398000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>111000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>147200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>210000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>138000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>161000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>131100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>275000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>429000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>455000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1417400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>498000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>366000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>328000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>326600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>451000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>301100</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>142600</v>
       </c>
-      <c r="E42" s="3">
-        <v>158000</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>165000</v>
       </c>
-      <c r="G42" s="3">
-        <v>193000</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>215800</v>
       </c>
-      <c r="I42" s="3">
-        <v>252000</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>279000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>315000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>380400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>368000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>11000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>39000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>15000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>22000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>564200</v>
-      </c>
-      <c r="U42" s="3">
-        <v>16000</v>
       </c>
       <c r="V42" s="3">
         <v>16000</v>
       </c>
       <c r="W42" s="3">
+        <v>16000</v>
+      </c>
+      <c r="X42" s="3">
         <v>22000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>33600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>72000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>78000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>51000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>49900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>28000</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
-      </c>
       <c r="AE42" s="3">
         <v>0</v>
       </c>
       <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
         <v>7100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>50000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>54000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>110000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>89500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>85000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>85300</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
         <v>90900</v>
       </c>
-      <c r="E43" s="3">
-        <v>97000</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3">
         <v>96000</v>
       </c>
-      <c r="G43" s="3">
-        <v>67000</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3">
         <v>150800</v>
       </c>
-      <c r="I43" s="3">
-        <v>80000</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="3">
         <v>75000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>53000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>78600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>52000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>48000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>530000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>63000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>55000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>99000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>44000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>47900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>33000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>31000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>29000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>39300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>34000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>32000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>33000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>35500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>43000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>31000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>35000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>44400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>383000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>280000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>289000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>296000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>271000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>266300</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4295,521 +4391,536 @@
         <v>0</v>
       </c>
       <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
         <v>83000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>82000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>89000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>91700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>87000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>2300</v>
       </c>
-      <c r="E45" s="3">
-        <v>41000</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>101000</v>
       </c>
-      <c r="G45" s="3">
-        <v>106000</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>19200</v>
       </c>
-      <c r="I45" s="3">
-        <v>45000</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>54000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>209000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>47200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>64000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>403000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>43000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>44000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>48000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>220000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>29000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>21400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>20000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>19000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>131000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>109500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>147000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>116000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>100000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>111100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>21000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>18000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>20000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>35800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>40000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>102000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>53000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>49800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>62000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>70800</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
         <v>1262700</v>
       </c>
-      <c r="E46" s="3">
-        <v>911000</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="3">
         <v>948000</v>
       </c>
-      <c r="G46" s="3">
-        <v>1043000</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="3">
         <v>1096000</v>
       </c>
-      <c r="I46" s="3">
-        <v>1010000</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K46" s="3">
         <v>998000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1327000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1061700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1034000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1299000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1291000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>582000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>865000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>644000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>550000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>919800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>501000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>464000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>293000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>329500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>463000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>364000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>345000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>327700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>367000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>478000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>510000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1504600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1054000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>884000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>869000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>853600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>956000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>809900</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
         <v>1458600</v>
       </c>
-      <c r="E47" s="3">
-        <v>693000</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>708000</v>
       </c>
-      <c r="G47" s="3">
-        <v>700000</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>703200</v>
       </c>
-      <c r="I47" s="3">
-        <v>696000</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>901000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>929000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1079400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1966000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1807000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1611000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1899000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1571000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1209000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1261000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>532400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>137000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>91000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>118000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>119700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>304000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>297000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>290000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>301200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>478000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>498000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>509000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>228400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>287000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>295000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>185000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>208200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>295000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>224800</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
         <v>1331700</v>
       </c>
-      <c r="E48" s="3">
-        <v>2108000</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3">
         <v>1937000</v>
       </c>
-      <c r="G48" s="3">
-        <v>1902000</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3">
         <v>1889300</v>
       </c>
-      <c r="I48" s="3">
-        <v>1771000</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K48" s="3">
         <v>1784000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1581000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1349200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1243000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1215000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1257000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1224000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1099000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1044000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1018000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>904600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>804000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>784000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>684000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>684800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>681000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>670000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>659000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>635100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>627000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>609000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>628000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>616200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3503000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3507000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3553000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3497300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3524000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3487300</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3">
         <v>71800</v>
       </c>
-      <c r="E49" s="3">
-        <v>307000</v>
-      </c>
-      <c r="F49" s="3">
-        <v>311000</v>
+      <c r="F49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G49" s="3">
         <v>311000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="3">
         <v>321300</v>
       </c>
-      <c r="I49" s="3">
-        <v>285000</v>
-      </c>
-      <c r="J49" s="3">
+      <c r="J49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K49" s="3">
         <v>288000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>245000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>220800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>222000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>219000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>223000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>225000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>208000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>214000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>217000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1500</v>
-      </c>
-      <c r="U49" s="3">
-        <v>1000</v>
       </c>
       <c r="V49" s="3">
         <v>1000</v>
@@ -4818,10 +4929,10 @@
         <v>1000</v>
       </c>
       <c r="X49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y49" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>1000</v>
       </c>
       <c r="Z49" s="3">
         <v>1000</v>
@@ -4830,10 +4941,10 @@
         <v>1000</v>
       </c>
       <c r="AB49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC49" s="3">
         <v>1300</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>2000</v>
       </c>
       <c r="AD49" s="3">
         <v>2000</v>
@@ -4842,28 +4953,31 @@
         <v>2000</v>
       </c>
       <c r="AF49" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AG49" s="3">
         <v>1600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>362000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>364000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>366000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>376800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>359000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>356200</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3">
         <v>47000</v>
       </c>
-      <c r="E52" s="3">
-        <v>83000</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>80000</v>
       </c>
-      <c r="G52" s="3">
-        <v>88000</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3">
         <v>38500</v>
       </c>
-      <c r="I52" s="3">
-        <v>145000</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>114000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>86000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>39800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>96000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>126000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>138000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>109000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>124000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>137000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>114000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>124100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>590000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>573000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>454000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>373100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>202000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>198000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>194000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>189800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>187000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>182000</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>175000</v>
       </c>
       <c r="AF52" s="3">
         <v>175000</v>
       </c>
       <c r="AG52" s="3">
+        <v>175000</v>
+      </c>
+      <c r="AH52" s="3">
         <v>153000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>161000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>212000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>201900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>129000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>176700</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3">
         <v>4213200</v>
       </c>
-      <c r="E54" s="3">
-        <v>4111000</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="3">
         <v>3994000</v>
       </c>
-      <c r="G54" s="3">
-        <v>4053000</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="3">
         <v>4108400</v>
       </c>
-      <c r="I54" s="3">
-        <v>3916000</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K54" s="3">
         <v>4091000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4173000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3772100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4561000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4666000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4520000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4039000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3867000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3248000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3160000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2482300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2033000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1913000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1550000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1508400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1651000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1530000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1489000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1455100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1661000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1769000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1824000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2525900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5359000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5211000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5185000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5137800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5263000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5054900</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,668 +5622,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>58300</v>
       </c>
-      <c r="E57" s="3">
-        <v>129000</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3">
         <v>198000</v>
       </c>
-      <c r="G57" s="3">
-        <v>179000</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3">
         <v>70700</v>
       </c>
-      <c r="I57" s="3">
-        <v>231000</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="3">
         <v>222000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>206000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>95000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>122000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>108000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>126000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>342500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>138000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>136000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>154000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>128200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>68000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>54000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>34000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>36000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>62000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>61000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>58000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>47700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>65000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>49000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>42000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>58900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>260000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>226000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>289000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>285600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>336000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>283300</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3">
         <v>88500</v>
       </c>
-      <c r="E58" s="3">
-        <v>110000</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="3">
         <v>108000</v>
       </c>
-      <c r="G58" s="3">
-        <v>114000</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" s="3">
         <v>174600</v>
       </c>
-      <c r="I58" s="3">
-        <v>130000</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="J58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K58" s="3">
         <v>106000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>99000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>56700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>54000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>51000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>41000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>38000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>429000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>50000</v>
       </c>
       <c r="S58" s="3">
         <v>50000</v>
       </c>
       <c r="T58" s="3">
+        <v>50000</v>
+      </c>
+      <c r="U58" s="3">
         <v>46500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>48000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>47000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>105000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>45600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>40000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>36000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>28000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>23200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>23000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>79000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>86000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>448000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>225000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>322000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>501000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>482800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>364000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>2700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>2000</v>
       </c>
-      <c r="F59" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>203000</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3">
         <v>10100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="J59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>152000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>23000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>574000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>26000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>426600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>45000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>34000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>28000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>53200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>33000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>27000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>25000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>23400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>36000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>16000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>28000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>19000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>17000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>106000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>125000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>299500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>179000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>213000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>251000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>276300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>343000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>332100</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3">
         <v>182800</v>
       </c>
-      <c r="E60" s="3">
-        <v>241000</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="3">
         <v>308000</v>
       </c>
-      <c r="G60" s="3">
-        <v>496000</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="3">
         <v>358800</v>
       </c>
-      <c r="I60" s="3">
-        <v>362000</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K60" s="3">
         <v>329000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>457000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>193000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>199000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>733000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>193000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>447000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>612000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>220000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>232000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>227900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>149000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>128000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>164000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>105000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>138000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>113000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>114000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>89900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>105000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>234000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>253000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>806300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>664000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>761000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1041000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1044800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1043000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>955200</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>1191600</v>
       </c>
-      <c r="E61" s="3">
-        <v>1421000</v>
-      </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>1412000</v>
       </c>
-      <c r="G61" s="3">
-        <v>1436000</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>1416900</v>
       </c>
-      <c r="I61" s="3">
-        <v>1309000</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>1325000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1223000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1144000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1101000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1117000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1192000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1172000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1094000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1042000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1001000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>871800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>714000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>688000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>555000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>576700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>586000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>582000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>575000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>563200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>585000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>564000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>584000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>588500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3344000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3170000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2892000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2829600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2941000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2820000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3">
         <v>31500</v>
       </c>
-      <c r="E62" s="3">
-        <v>178000</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3">
         <v>168000</v>
       </c>
-      <c r="G62" s="3">
-        <v>126000</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3">
         <v>46900</v>
       </c>
-      <c r="I62" s="3">
-        <v>41000</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>39000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>43000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>41400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>151000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>177000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>174000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>168000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>151000</v>
-      </c>
-      <c r="R62" s="3">
-        <v>156000</v>
       </c>
       <c r="S62" s="3">
         <v>156000</v>
       </c>
       <c r="T62" s="3">
+        <v>156000</v>
+      </c>
+      <c r="U62" s="3">
         <v>106600</v>
-      </c>
-      <c r="U62" s="3">
-        <v>124000</v>
       </c>
       <c r="V62" s="3">
         <v>124000</v>
       </c>
       <c r="W62" s="3">
+        <v>124000</v>
+      </c>
+      <c r="X62" s="3">
         <v>121000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>114900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>109000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>102000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>99000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>86200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>88000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>84000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>85000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>79600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>360000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>375000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>363000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>369200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>345000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>336300</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3">
         <v>1553700</v>
       </c>
-      <c r="E66" s="3">
-        <v>1978000</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="3">
         <v>2018000</v>
       </c>
-      <c r="G66" s="3">
-        <v>2190000</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="3">
         <v>2038200</v>
       </c>
-      <c r="I66" s="3">
-        <v>1849000</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K66" s="3">
         <v>1822000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1853000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1476100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2128000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2534000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2084000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2245000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2286000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1858000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1846000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1415500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1073000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1022000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>921000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>885000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>936000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>879000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>855000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>806100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>848000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>949000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>997000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1542700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4622000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4522000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4514000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4456600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4545000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4321100</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>1491200</v>
       </c>
-      <c r="E72" s="3">
-        <v>1051000</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3">
         <v>1007000</v>
       </c>
-      <c r="G72" s="3">
-        <v>895000</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3">
         <v>1087000</v>
       </c>
-      <c r="I72" s="3">
-        <v>1083000</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" s="3">
         <v>1303000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1349000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1504600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2384000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2079000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1814000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1166000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>960000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>770000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>699000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>448500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>360000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>293000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>11000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>92000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>42000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>33000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>45800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>207000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>229000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>258000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-282500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-531000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-575000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-584000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-564500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-533000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-513100</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3">
         <v>1607900</v>
       </c>
-      <c r="E76" s="3">
-        <v>1164000</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="3">
         <v>1117000</v>
       </c>
-      <c r="G76" s="3">
-        <v>1006000</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" s="3">
         <v>1203300</v>
       </c>
-      <c r="I76" s="3">
-        <v>1200000</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K76" s="3">
         <v>1420000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1470000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1598500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2433000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2132000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2436000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1794000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1581000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1390000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1314000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1066800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>960000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>891000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>629000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>623400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>715000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>651000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>634000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>649000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>813000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>820000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>827000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>983100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>737000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>689000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>671000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>681200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>718000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>733800</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
         <v>434700</v>
       </c>
-      <c r="E81" s="3">
-        <v>43000</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3">
         <v>112000</v>
       </c>
-      <c r="G81" s="3">
-        <v>8000</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3">
         <v>7000</v>
       </c>
-      <c r="I81" s="3">
-        <v>-205000</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>-30000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-842300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>251000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>265000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>639000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>392300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>538000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>172000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>180000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>145100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>67000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>279000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>15000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-23400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>28000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-61800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-29000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>545000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>236600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-23000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>9000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-411900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-48000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-281400</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>10800</v>
       </c>
-      <c r="E83" s="3">
-        <v>28000</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
         <v>23000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
         <v>15000</v>
       </c>
-      <c r="H83" s="3">
-        <v>7300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>15000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>15000</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3400</v>
-      </c>
-      <c r="M83" s="3">
-        <v>15000</v>
       </c>
       <c r="N83" s="3">
         <v>15000</v>
       </c>
       <c r="O83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="P83" s="3">
         <v>14000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>14600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>43000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>16000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>11200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>9000</v>
-      </c>
-      <c r="V83" s="3">
-        <v>7000</v>
       </c>
       <c r="W83" s="3">
         <v>7000</v>
       </c>
       <c r="X83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Y83" s="3">
         <v>9100</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>8000</v>
       </c>
       <c r="Z83" s="3">
         <v>8000</v>
       </c>
       <c r="AA83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="AB83" s="3">
         <v>7000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>7400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>7000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>8000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>178500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>43000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>44000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>48000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>172400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>48200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>41900</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>52100</v>
       </c>
-      <c r="E89" s="3">
-        <v>126000</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>17000</v>
       </c>
-      <c r="G89" s="3">
-        <v>70000</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
         <v>11800</v>
       </c>
-      <c r="I89" s="3">
-        <v>76000</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>163000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>26000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>48400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>163000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>542000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>18000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>107500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>133000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>28000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>35000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>33000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>15000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>35000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>47000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>163400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>10000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>13000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-134000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>391900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>40000</v>
-      </c>
-      <c r="AH89" s="3">
-        <v>101000</v>
       </c>
       <c r="AI89" s="3">
         <v>101000</v>
       </c>
       <c r="AJ89" s="3">
+        <v>101000</v>
+      </c>
+      <c r="AK89" s="3">
         <v>162300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>65600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>52300</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15700</v>
       </c>
-      <c r="E91" s="3">
-        <v>-188000</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3">
         <v>-68000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-69000</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-133100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-65300</v>
+      </c>
+      <c r="N91" s="3">
         <v>-60000</v>
       </c>
-      <c r="J91" s="3">
-        <v>-86000</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-53000</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-65300</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-60000</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-78000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-87000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-80700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-61000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-46000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-45000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-24500</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-11000</v>
       </c>
       <c r="V91" s="3">
         <v>-11000</v>
       </c>
       <c r="W91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="X91" s="3">
         <v>-28000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-36300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-227600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-60000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-40000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-290600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-103300</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>240900</v>
       </c>
-      <c r="E94" s="3">
-        <v>-142000</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3">
         <v>72000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-35000</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>-118200</v>
       </c>
-      <c r="I94" s="3">
-        <v>-42000</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3">
         <v>-241000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-31000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-70400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-80000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-430000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>377000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-61500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-144000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-52000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-98000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-327600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-16000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>211000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-89000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>50000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>3000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-46000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-197400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-115000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>217000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>584500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>3000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-62000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-114000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-399600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-36300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-167400</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,65 +9520,66 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3">
         <v>201000</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
         <v>400</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>150000</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3">
         <v>-552000</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-189000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-100000</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-114100</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>105900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-178000</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3">
+        <v>166600</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-78000</v>
+      </c>
+      <c r="L100" s="3">
+        <v>220000</v>
+      </c>
+      <c r="M100" s="3">
+        <v>4300</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-369000</v>
+      </c>
+      <c r="O100" s="3">
+        <v>21000</v>
+      </c>
+      <c r="P100" s="3">
+        <v>-150000</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>-304400</v>
+      </c>
+      <c r="R100" s="3">
+        <v>451000</v>
+      </c>
+      <c r="S100" s="3">
+        <v>-129000</v>
+      </c>
+      <c r="T100" s="3">
+        <v>254000</v>
+      </c>
+      <c r="U100" s="3">
+        <v>162800</v>
+      </c>
+      <c r="V100" s="3">
+        <v>13000</v>
+      </c>
+      <c r="W100" s="3">
         <v>44000</v>
       </c>
-      <c r="F100" s="3">
-        <v>-178000</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-56000</v>
-      </c>
-      <c r="H100" s="3">
-        <v>166600</v>
-      </c>
-      <c r="I100" s="3">
-        <v>16000</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-78000</v>
-      </c>
-      <c r="K100" s="3">
-        <v>220000</v>
-      </c>
-      <c r="L100" s="3">
-        <v>4300</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-369000</v>
-      </c>
-      <c r="N100" s="3">
-        <v>21000</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-150000</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-304400</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>451000</v>
-      </c>
-      <c r="R100" s="3">
-        <v>-129000</v>
-      </c>
-      <c r="S100" s="3">
-        <v>254000</v>
-      </c>
-      <c r="T100" s="3">
-        <v>162800</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="X100" s="3">
+        <v>36000</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>-109600</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AA100" s="3">
         <v>13000</v>
       </c>
-      <c r="V100" s="3">
-        <v>44000</v>
-      </c>
-      <c r="W100" s="3">
-        <v>36000</v>
-      </c>
-      <c r="X100" s="3">
-        <v>-109600</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>31000</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>13000</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-108600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-50000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1049000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>97100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>90000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>174600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>119200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>3500</v>
       </c>
-      <c r="E101" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3">
         <v>3400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="M101" s="3">
+        <v>9700</v>
+      </c>
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="O101" s="3">
         <v>-10000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="P101" s="3">
         <v>-6000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="Q101" s="3">
         <v>9700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="R101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="S101" s="3">
+        <v>8000</v>
+      </c>
+      <c r="T101" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="U101" s="3">
+        <v>9600</v>
+      </c>
+      <c r="V101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="X101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>17300</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="P101" s="3">
-        <v>9700</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>8000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="T101" s="3">
-        <v>9600</v>
-      </c>
-      <c r="U101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="AI101" s="3">
         <v>3000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="AJ101" s="3">
+        <v>11000</v>
+      </c>
+      <c r="AK101" s="3">
+        <v>5400</v>
+      </c>
+      <c r="AL101" s="3">
         <v>1300</v>
       </c>
-      <c r="Y101" s="3">
-        <v>3000</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>4000</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>17300</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AI101" s="3">
-        <v>11000</v>
-      </c>
-      <c r="AJ101" s="3">
-        <v>5400</v>
-      </c>
-      <c r="AK101" s="3">
-        <v>1300</v>
-      </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>401000</v>
       </c>
-      <c r="E102" s="3">
-        <v>29000</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-91000</v>
       </c>
-      <c r="G102" s="3">
-        <v>-20000</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>63700</v>
       </c>
-      <c r="I102" s="3">
-        <v>43000</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-160000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>215000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-287000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>123000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>239000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-248600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>437000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-145000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>169000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-146000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>34000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>286000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-35000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-63000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>72000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-23000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>30000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-144300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-154000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-26000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-962000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1090800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>132000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>38000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-57300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>149900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-87500</v>
       </c>
     </row>
